--- a/템플릿/조달청50억~100억.xlsx
+++ b/템플릿/조달청50억~100억.xlsx
@@ -1399,6 +1399,105 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="41" fontId="7" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1427,105 +1526,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="11" fillId="2" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1827,14 +1827,15 @@
     <col min="15" max="15" width="5.109375" style="1" customWidth="1"/>
     <col min="16" max="16" width="7.109375" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.77734375" style="1" customWidth="1"/>
-    <col min="18" max="20" width="6.6640625" style="1" customWidth="1"/>
+    <col min="18" max="19" width="6.6640625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="1" customWidth="1"/>
     <col min="21" max="21" width="7.109375" style="1" customWidth="1"/>
     <col min="22" max="22" width="8.88671875" style="2" hidden="1" customWidth="1"/>
     <col min="23" max="24" width="8" style="1" customWidth="1"/>
     <col min="25" max="25" width="8.21875" style="1" customWidth="1"/>
     <col min="26" max="26" width="7.77734375" style="1" customWidth="1"/>
     <col min="27" max="27" width="7.21875" style="1" customWidth="1"/>
-    <col min="28" max="28" width="7.44140625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="8.6640625" style="1" customWidth="1"/>
     <col min="29" max="29" width="8.77734375" style="2" hidden="1" customWidth="1"/>
     <col min="30" max="30" width="5.21875" style="1" customWidth="1"/>
     <col min="31" max="32" width="6.21875" style="1" customWidth="1"/>
@@ -1843,7 +1844,8 @@
     <col min="35" max="35" width="8.21875" style="1" customWidth="1"/>
     <col min="36" max="36" width="8.77734375" style="1" customWidth="1"/>
     <col min="37" max="37" width="7.5546875" style="1" customWidth="1"/>
-    <col min="38" max="39" width="8.33203125" style="1" customWidth="1"/>
+    <col min="38" max="38" width="8.33203125" style="1" customWidth="1"/>
+    <col min="39" max="39" width="10.33203125" style="1" customWidth="1"/>
     <col min="40" max="40" width="20.21875" style="1" customWidth="1"/>
     <col min="41" max="41" width="8.33203125" style="1" customWidth="1"/>
     <col min="42" max="47" width="17.6640625" style="1" customWidth="1"/>
@@ -1854,52 +1856,52 @@
       <c r="C1" s="103" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
       <c r="F1" s="101"/>
       <c r="G1" s="101"/>
       <c r="H1" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="115">
+      <c r="I1" s="148">
         <v>4228600000</v>
       </c>
-      <c r="J1" s="115"/>
+      <c r="J1" s="148"/>
       <c r="K1" s="109" t="e">
         <f>TRUNC(I1/F2,7)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L1" s="108"/>
       <c r="M1" s="107"/>
-      <c r="N1" s="116" t="s">
+      <c r="N1" s="149" t="s">
         <v>46</v>
       </c>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="116"/>
-      <c r="Y1" s="116"/>
-      <c r="Z1" s="116"/>
-      <c r="AA1" s="116"/>
-      <c r="AB1" s="116"/>
-      <c r="AC1" s="116"/>
-      <c r="AD1" s="116"/>
-      <c r="AE1" s="116"/>
-      <c r="AF1" s="116"/>
-      <c r="AG1" s="116"/>
-      <c r="AH1" s="116"/>
-      <c r="AI1" s="117" t="s">
+      <c r="O1" s="149"/>
+      <c r="P1" s="149"/>
+      <c r="Q1" s="149"/>
+      <c r="R1" s="149"/>
+      <c r="S1" s="149"/>
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="149"/>
+      <c r="W1" s="149"/>
+      <c r="X1" s="149"/>
+      <c r="Y1" s="149"/>
+      <c r="Z1" s="149"/>
+      <c r="AA1" s="149"/>
+      <c r="AB1" s="149"/>
+      <c r="AC1" s="149"/>
+      <c r="AD1" s="149"/>
+      <c r="AE1" s="149"/>
+      <c r="AF1" s="149"/>
+      <c r="AG1" s="149"/>
+      <c r="AH1" s="149"/>
+      <c r="AI1" s="150" t="s">
         <v>48</v>
       </c>
-      <c r="AJ1" s="117"/>
-      <c r="AK1" s="117"/>
-      <c r="AL1" s="117"/>
+      <c r="AJ1" s="150"/>
+      <c r="AK1" s="150"/>
+      <c r="AL1" s="150"/>
       <c r="AM1" s="106"/>
       <c r="AN1" s="106"/>
       <c r="AO1" s="106"/>
@@ -1910,21 +1912,21 @@
       <c r="C2" s="104" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="118">
+      <c r="D2" s="151">
         <f>D1*1.1</f>
         <v>0</v>
       </c>
-      <c r="E2" s="119"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="119"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="152"/>
       <c r="H2" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="120">
+      <c r="I2" s="153">
         <f>D2*2</f>
         <v>0</v>
       </c>
-      <c r="J2" s="121"/>
+      <c r="J2" s="154"/>
       <c r="K2" s="102" t="s">
         <v>38</v>
       </c>
@@ -1934,14 +1936,14 @@
       <c r="O2" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="122" t="s">
+      <c r="P2" s="155" t="s">
         <v>47</v>
       </c>
-      <c r="Q2" s="123"/>
-      <c r="R2" s="123"/>
-      <c r="S2" s="123"/>
-      <c r="T2" s="123"/>
-      <c r="U2" s="123"/>
+      <c r="Q2" s="156"/>
+      <c r="R2" s="156"/>
+      <c r="S2" s="156"/>
+      <c r="T2" s="156"/>
+      <c r="U2" s="156"/>
       <c r="V2" s="99"/>
       <c r="W2" s="99"/>
       <c r="X2" s="98"/>
@@ -1972,50 +1974,50 @@
       <c r="AU2" s="90"/>
     </row>
     <row r="3" spans="1:47" s="5" customFormat="1" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A3" s="124" t="s">
+      <c r="A3" s="132" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="126" t="s">
+      <c r="B3" s="134" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="128" t="s">
+      <c r="C3" s="136" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="128" t="s">
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="136" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="131" t="s">
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
+      <c r="L3" s="137"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="139" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="133" t="s">
+      <c r="O3" s="141" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="128" t="s">
+      <c r="P3" s="136" t="s">
         <v>29</v>
       </c>
-      <c r="Q3" s="129"/>
-      <c r="R3" s="129"/>
-      <c r="S3" s="129"/>
-      <c r="T3" s="129"/>
-      <c r="U3" s="130"/>
+      <c r="Q3" s="137"/>
+      <c r="R3" s="137"/>
+      <c r="S3" s="137"/>
+      <c r="T3" s="137"/>
+      <c r="U3" s="138"/>
       <c r="V3" s="113"/>
-      <c r="W3" s="128" t="s">
+      <c r="W3" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="X3" s="129"/>
-      <c r="Y3" s="129"/>
-      <c r="Z3" s="129"/>
-      <c r="AA3" s="129"/>
-      <c r="AB3" s="130"/>
+      <c r="X3" s="137"/>
+      <c r="Y3" s="137"/>
+      <c r="Z3" s="137"/>
+      <c r="AA3" s="137"/>
+      <c r="AB3" s="138"/>
       <c r="AC3" s="113"/>
       <c r="AD3" s="113"/>
       <c r="AE3" s="88" t="s">
@@ -2025,46 +2027,46 @@
       <c r="AG3" s="113"/>
       <c r="AH3" s="113"/>
       <c r="AI3" s="87"/>
-      <c r="AJ3" s="135" t="s">
+      <c r="AJ3" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="AK3" s="126" t="s">
+      <c r="AK3" s="134" t="s">
         <v>26</v>
       </c>
-      <c r="AL3" s="137" t="s">
+      <c r="AL3" s="145" t="s">
         <v>25</v>
       </c>
-      <c r="AM3" s="139" t="s">
+      <c r="AM3" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="AN3" s="142" t="s">
+      <c r="AN3" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="AO3" s="144" t="s">
+      <c r="AO3" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="AP3" s="146" t="s">
+      <c r="AP3" s="127" t="s">
         <v>21</v>
       </c>
-      <c r="AQ3" s="148" t="s">
+      <c r="AQ3" s="129" t="s">
         <v>20</v>
       </c>
-      <c r="AR3" s="141" t="s">
+      <c r="AR3" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="AS3" s="141" t="s">
+      <c r="AS3" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="AT3" s="141" t="s">
+      <c r="AT3" s="122" t="s">
         <v>17</v>
       </c>
-      <c r="AU3" s="141" t="s">
+      <c r="AU3" s="122" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:47" s="5" customFormat="1" ht="39.75" customHeight="1" thickBot="1">
-      <c r="A4" s="125"/>
-      <c r="B4" s="127"/>
+      <c r="A4" s="133"/>
+      <c r="B4" s="135"/>
       <c r="C4" s="84" t="s">
         <v>12</v>
       </c>
@@ -2098,8 +2100,8 @@
       <c r="M4" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="132"/>
-      <c r="O4" s="134"/>
+      <c r="N4" s="140"/>
+      <c r="O4" s="142"/>
       <c r="P4" s="84" t="s">
         <v>12</v>
       </c>
@@ -2160,18 +2162,18 @@
       <c r="AI4" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="AJ4" s="136"/>
-      <c r="AK4" s="127"/>
-      <c r="AL4" s="138"/>
-      <c r="AM4" s="140"/>
-      <c r="AN4" s="143"/>
-      <c r="AO4" s="145"/>
-      <c r="AP4" s="147"/>
-      <c r="AQ4" s="141"/>
-      <c r="AR4" s="141"/>
-      <c r="AS4" s="141"/>
-      <c r="AT4" s="141"/>
-      <c r="AU4" s="141"/>
+      <c r="AJ4" s="144"/>
+      <c r="AK4" s="135"/>
+      <c r="AL4" s="146"/>
+      <c r="AM4" s="131"/>
+      <c r="AN4" s="124"/>
+      <c r="AO4" s="126"/>
+      <c r="AP4" s="128"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="122"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="122"/>
+      <c r="AU4" s="122"/>
     </row>
     <row r="5" spans="1:47" s="37" customFormat="1" ht="45.75" customHeight="1" thickBot="1">
       <c r="A5" s="36"/>
@@ -2182,9 +2184,9 @@
       <c r="F5" s="46"/>
       <c r="G5" s="45"/>
       <c r="H5" s="110"/>
-      <c r="I5" s="150"/>
-      <c r="J5" s="151"/>
-      <c r="K5" s="152"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="116"/>
+      <c r="K5" s="117"/>
       <c r="L5" s="31"/>
       <c r="M5" s="28"/>
       <c r="N5" s="27">
@@ -2270,9 +2272,9 @@
       <c r="F6" s="46"/>
       <c r="G6" s="45"/>
       <c r="H6" s="110"/>
-      <c r="I6" s="150"/>
-      <c r="J6" s="151"/>
-      <c r="K6" s="152"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="116"/>
+      <c r="K6" s="117"/>
       <c r="L6" s="31"/>
       <c r="M6" s="28"/>
       <c r="N6" s="27">
@@ -2358,9 +2360,9 @@
       <c r="F7" s="46"/>
       <c r="G7" s="45"/>
       <c r="H7" s="111"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="153"/>
-      <c r="K7" s="153"/>
+      <c r="I7" s="115"/>
+      <c r="J7" s="118"/>
+      <c r="K7" s="118"/>
       <c r="L7" s="29"/>
       <c r="M7" s="28"/>
       <c r="N7" s="27">
@@ -2446,9 +2448,9 @@
       <c r="F8" s="46"/>
       <c r="G8" s="45"/>
       <c r="H8" s="110"/>
-      <c r="I8" s="150"/>
-      <c r="J8" s="153"/>
-      <c r="K8" s="152"/>
+      <c r="I8" s="115"/>
+      <c r="J8" s="118"/>
+      <c r="K8" s="117"/>
       <c r="L8" s="31"/>
       <c r="M8" s="28"/>
       <c r="N8" s="27">
@@ -2534,9 +2536,9 @@
       <c r="F9" s="47"/>
       <c r="G9" s="45"/>
       <c r="H9" s="110"/>
-      <c r="I9" s="150"/>
-      <c r="J9" s="153"/>
-      <c r="K9" s="152"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="117"/>
       <c r="L9" s="31"/>
       <c r="M9" s="28"/>
       <c r="N9" s="27">
@@ -2622,9 +2624,9 @@
       <c r="F10" s="47"/>
       <c r="G10" s="45"/>
       <c r="H10" s="45"/>
-      <c r="I10" s="150"/>
-      <c r="J10" s="153"/>
-      <c r="K10" s="152"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="118"/>
+      <c r="K10" s="117"/>
       <c r="L10" s="31"/>
       <c r="M10" s="28"/>
       <c r="N10" s="27">
@@ -2713,9 +2715,9 @@
       <c r="F11" s="47"/>
       <c r="G11" s="38"/>
       <c r="H11" s="32"/>
-      <c r="I11" s="150"/>
-      <c r="J11" s="153"/>
-      <c r="K11" s="152"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="118"/>
+      <c r="K11" s="117"/>
       <c r="L11" s="29"/>
       <c r="M11" s="28"/>
       <c r="N11" s="27">
@@ -2801,9 +2803,9 @@
       <c r="F12" s="34"/>
       <c r="G12" s="45"/>
       <c r="H12" s="45"/>
-      <c r="I12" s="150"/>
-      <c r="J12" s="153"/>
-      <c r="K12" s="153"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="118"/>
       <c r="L12" s="30"/>
       <c r="M12" s="51"/>
       <c r="N12" s="27">
@@ -2889,9 +2891,9 @@
       <c r="F13" s="47"/>
       <c r="G13" s="38"/>
       <c r="H13" s="45"/>
-      <c r="I13" s="150"/>
-      <c r="J13" s="153"/>
-      <c r="K13" s="152"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="118"/>
+      <c r="K13" s="117"/>
       <c r="L13" s="31"/>
       <c r="M13" s="28"/>
       <c r="N13" s="27">
@@ -2977,9 +2979,9 @@
       <c r="F14" s="47"/>
       <c r="G14" s="45"/>
       <c r="H14" s="56"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="154"/>
-      <c r="K14" s="155"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="119"/>
+      <c r="K14" s="120"/>
       <c r="L14" s="72"/>
       <c r="M14" s="71"/>
       <c r="N14" s="27">
@@ -3065,9 +3067,9 @@
       <c r="F15" s="34"/>
       <c r="G15" s="45"/>
       <c r="H15" s="45"/>
-      <c r="I15" s="150"/>
-      <c r="J15" s="153"/>
-      <c r="K15" s="152"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="118"/>
+      <c r="K15" s="117"/>
       <c r="L15" s="29"/>
       <c r="M15" s="28"/>
       <c r="N15" s="27">
@@ -3153,9 +3155,9 @@
       <c r="F16" s="112"/>
       <c r="G16" s="38"/>
       <c r="H16" s="32"/>
-      <c r="I16" s="150"/>
-      <c r="J16" s="153"/>
-      <c r="K16" s="152"/>
+      <c r="I16" s="115"/>
+      <c r="J16" s="118"/>
+      <c r="K16" s="117"/>
       <c r="L16" s="29"/>
       <c r="M16" s="28"/>
       <c r="N16" s="27">
@@ -3241,9 +3243,9 @@
       <c r="F17" s="58"/>
       <c r="G17" s="57"/>
       <c r="H17" s="56"/>
-      <c r="I17" s="150"/>
-      <c r="J17" s="153"/>
-      <c r="K17" s="152"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="118"/>
+      <c r="K17" s="117"/>
       <c r="L17" s="31"/>
       <c r="M17" s="28"/>
       <c r="N17" s="27">
@@ -3329,9 +3331,9 @@
       <c r="F18" s="47"/>
       <c r="G18" s="45"/>
       <c r="H18" s="45"/>
-      <c r="I18" s="150"/>
-      <c r="J18" s="153"/>
-      <c r="K18" s="152"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="118"/>
+      <c r="K18" s="117"/>
       <c r="L18" s="31"/>
       <c r="M18" s="28"/>
       <c r="N18" s="27">
@@ -3417,9 +3419,9 @@
       <c r="F19" s="46"/>
       <c r="G19" s="45"/>
       <c r="H19" s="45"/>
-      <c r="I19" s="150"/>
-      <c r="J19" s="153"/>
-      <c r="K19" s="152"/>
+      <c r="I19" s="115"/>
+      <c r="J19" s="118"/>
+      <c r="K19" s="117"/>
       <c r="L19" s="31"/>
       <c r="M19" s="28"/>
       <c r="N19" s="27">
@@ -3505,9 +3507,9 @@
       <c r="F20" s="34"/>
       <c r="G20" s="38"/>
       <c r="H20" s="32"/>
-      <c r="I20" s="150"/>
-      <c r="J20" s="156"/>
-      <c r="K20" s="152"/>
+      <c r="I20" s="115"/>
+      <c r="J20" s="121"/>
+      <c r="K20" s="117"/>
       <c r="L20" s="29"/>
       <c r="M20" s="28"/>
       <c r="N20" s="27">
@@ -3596,9 +3598,9 @@
       <c r="F21" s="46"/>
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
-      <c r="I21" s="150"/>
-      <c r="J21" s="153"/>
-      <c r="K21" s="153"/>
+      <c r="I21" s="115"/>
+      <c r="J21" s="118"/>
+      <c r="K21" s="118"/>
       <c r="L21" s="30"/>
       <c r="M21" s="51"/>
       <c r="N21" s="27">
@@ -3684,9 +3686,9 @@
       <c r="F22" s="34"/>
       <c r="G22" s="38"/>
       <c r="H22" s="32"/>
-      <c r="I22" s="150"/>
-      <c r="J22" s="153"/>
-      <c r="K22" s="152"/>
+      <c r="I22" s="115"/>
+      <c r="J22" s="118"/>
+      <c r="K22" s="117"/>
       <c r="L22" s="29"/>
       <c r="M22" s="28"/>
       <c r="N22" s="27">
@@ -3772,9 +3774,9 @@
       <c r="F23" s="34"/>
       <c r="G23" s="38"/>
       <c r="H23" s="45"/>
-      <c r="I23" s="150"/>
-      <c r="J23" s="153"/>
-      <c r="K23" s="153"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="118"/>
+      <c r="K23" s="118"/>
       <c r="L23" s="29"/>
       <c r="M23" s="28"/>
       <c r="N23" s="27">
@@ -3860,9 +3862,9 @@
       <c r="F24" s="34"/>
       <c r="G24" s="38"/>
       <c r="H24" s="32"/>
-      <c r="I24" s="150"/>
-      <c r="J24" s="153"/>
-      <c r="K24" s="152"/>
+      <c r="I24" s="115"/>
+      <c r="J24" s="118"/>
+      <c r="K24" s="117"/>
       <c r="L24" s="29"/>
       <c r="M24" s="28"/>
       <c r="N24" s="27">
@@ -3948,9 +3950,9 @@
       <c r="F25" s="46"/>
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
-      <c r="I25" s="150"/>
-      <c r="J25" s="153"/>
-      <c r="K25" s="152"/>
+      <c r="I25" s="115"/>
+      <c r="J25" s="118"/>
+      <c r="K25" s="117"/>
       <c r="L25" s="29"/>
       <c r="M25" s="28"/>
       <c r="N25" s="27">
@@ -4038,9 +4040,9 @@
       <c r="F26" s="46"/>
       <c r="G26" s="45"/>
       <c r="H26" s="45"/>
-      <c r="I26" s="150"/>
-      <c r="J26" s="153"/>
-      <c r="K26" s="152"/>
+      <c r="I26" s="115"/>
+      <c r="J26" s="118"/>
+      <c r="K26" s="117"/>
       <c r="L26" s="31"/>
       <c r="M26" s="28"/>
       <c r="N26" s="27">
@@ -4126,9 +4128,9 @@
       <c r="F27" s="34"/>
       <c r="G27" s="38"/>
       <c r="H27" s="32"/>
-      <c r="I27" s="150"/>
-      <c r="J27" s="153"/>
-      <c r="K27" s="152"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="118"/>
+      <c r="K27" s="117"/>
       <c r="L27" s="29"/>
       <c r="M27" s="28"/>
       <c r="N27" s="27">
@@ -4214,9 +4216,9 @@
       <c r="F28" s="34"/>
       <c r="G28" s="38"/>
       <c r="H28" s="32"/>
-      <c r="I28" s="150"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="152"/>
+      <c r="I28" s="115"/>
+      <c r="J28" s="118"/>
+      <c r="K28" s="117"/>
       <c r="L28" s="29"/>
       <c r="M28" s="28"/>
       <c r="N28" s="27">
@@ -4302,9 +4304,9 @@
       <c r="F29" s="34"/>
       <c r="G29" s="38"/>
       <c r="H29" s="32"/>
-      <c r="I29" s="150"/>
-      <c r="J29" s="153"/>
-      <c r="K29" s="152"/>
+      <c r="I29" s="115"/>
+      <c r="J29" s="118"/>
+      <c r="K29" s="117"/>
       <c r="L29" s="29"/>
       <c r="M29" s="28"/>
       <c r="N29" s="27">
@@ -4393,9 +4395,9 @@
       <c r="F30" s="34"/>
       <c r="G30" s="38"/>
       <c r="H30" s="32"/>
-      <c r="I30" s="150"/>
-      <c r="J30" s="153"/>
-      <c r="K30" s="152"/>
+      <c r="I30" s="115"/>
+      <c r="J30" s="118"/>
+      <c r="K30" s="117"/>
       <c r="L30" s="29"/>
       <c r="M30" s="28"/>
       <c r="N30" s="27">
@@ -4481,9 +4483,9 @@
       <c r="F31" s="34"/>
       <c r="G31" s="38"/>
       <c r="H31" s="32"/>
-      <c r="I31" s="150"/>
-      <c r="J31" s="153"/>
-      <c r="K31" s="152"/>
+      <c r="I31" s="115"/>
+      <c r="J31" s="118"/>
+      <c r="K31" s="117"/>
       <c r="L31" s="29"/>
       <c r="M31" s="28"/>
       <c r="N31" s="27">
@@ -4569,9 +4571,9 @@
       <c r="F32" s="34"/>
       <c r="G32" s="38"/>
       <c r="H32" s="32"/>
-      <c r="I32" s="150"/>
-      <c r="J32" s="153"/>
-      <c r="K32" s="152"/>
+      <c r="I32" s="115"/>
+      <c r="J32" s="118"/>
+      <c r="K32" s="117"/>
       <c r="L32" s="29"/>
       <c r="M32" s="28"/>
       <c r="N32" s="27">
@@ -4657,9 +4659,9 @@
       <c r="F33" s="34"/>
       <c r="G33" s="38"/>
       <c r="H33" s="32"/>
-      <c r="I33" s="150"/>
-      <c r="J33" s="153"/>
-      <c r="K33" s="152"/>
+      <c r="I33" s="115"/>
+      <c r="J33" s="118"/>
+      <c r="K33" s="117"/>
       <c r="L33" s="29"/>
       <c r="M33" s="28"/>
       <c r="N33" s="27">
@@ -4745,9 +4747,9 @@
       <c r="F34" s="34"/>
       <c r="G34" s="38"/>
       <c r="H34" s="32"/>
-      <c r="I34" s="150"/>
-      <c r="J34" s="153"/>
-      <c r="K34" s="152"/>
+      <c r="I34" s="115"/>
+      <c r="J34" s="118"/>
+      <c r="K34" s="117"/>
       <c r="L34" s="29"/>
       <c r="M34" s="28"/>
       <c r="N34" s="27">
@@ -4833,9 +4835,9 @@
       <c r="F35" s="34"/>
       <c r="G35" s="38"/>
       <c r="H35" s="32"/>
-      <c r="I35" s="150"/>
-      <c r="J35" s="153"/>
-      <c r="K35" s="152"/>
+      <c r="I35" s="115"/>
+      <c r="J35" s="118"/>
+      <c r="K35" s="117"/>
       <c r="L35" s="29"/>
       <c r="M35" s="28"/>
       <c r="N35" s="27">
@@ -4921,9 +4923,9 @@
       <c r="F36" s="34"/>
       <c r="G36" s="38"/>
       <c r="H36" s="32"/>
-      <c r="I36" s="150"/>
-      <c r="J36" s="153"/>
-      <c r="K36" s="152"/>
+      <c r="I36" s="115"/>
+      <c r="J36" s="118"/>
+      <c r="K36" s="117"/>
       <c r="L36" s="29"/>
       <c r="M36" s="28"/>
       <c r="N36" s="27">
@@ -5009,9 +5011,9 @@
       <c r="F37" s="34"/>
       <c r="G37" s="38"/>
       <c r="H37" s="32"/>
-      <c r="I37" s="150"/>
-      <c r="J37" s="153"/>
-      <c r="K37" s="152"/>
+      <c r="I37" s="115"/>
+      <c r="J37" s="118"/>
+      <c r="K37" s="117"/>
       <c r="L37" s="29"/>
       <c r="M37" s="28"/>
       <c r="N37" s="27">
@@ -5099,9 +5101,9 @@
       <c r="F38" s="34"/>
       <c r="G38" s="38"/>
       <c r="H38" s="32"/>
-      <c r="I38" s="150"/>
-      <c r="J38" s="153"/>
-      <c r="K38" s="152"/>
+      <c r="I38" s="115"/>
+      <c r="J38" s="118"/>
+      <c r="K38" s="117"/>
       <c r="L38" s="29"/>
       <c r="M38" s="28"/>
       <c r="N38" s="27">
@@ -5187,9 +5189,9 @@
       <c r="F39" s="34"/>
       <c r="G39" s="38"/>
       <c r="H39" s="32"/>
-      <c r="I39" s="150"/>
-      <c r="J39" s="153"/>
-      <c r="K39" s="152"/>
+      <c r="I39" s="115"/>
+      <c r="J39" s="118"/>
+      <c r="K39" s="117"/>
       <c r="L39" s="29"/>
       <c r="M39" s="28"/>
       <c r="N39" s="27">
@@ -5275,9 +5277,9 @@
       <c r="F40" s="34"/>
       <c r="G40" s="38"/>
       <c r="H40" s="32"/>
-      <c r="I40" s="150"/>
-      <c r="J40" s="153"/>
-      <c r="K40" s="152"/>
+      <c r="I40" s="115"/>
+      <c r="J40" s="118"/>
+      <c r="K40" s="117"/>
       <c r="L40" s="29"/>
       <c r="M40" s="28"/>
       <c r="N40" s="27">
@@ -5363,9 +5365,9 @@
       <c r="F41" s="34"/>
       <c r="G41" s="38"/>
       <c r="H41" s="32"/>
-      <c r="I41" s="150"/>
-      <c r="J41" s="153"/>
-      <c r="K41" s="152"/>
+      <c r="I41" s="115"/>
+      <c r="J41" s="118"/>
+      <c r="K41" s="117"/>
       <c r="L41" s="29"/>
       <c r="M41" s="28"/>
       <c r="N41" s="27">
@@ -5451,9 +5453,9 @@
       <c r="F42" s="34"/>
       <c r="G42" s="38"/>
       <c r="H42" s="32"/>
-      <c r="I42" s="150"/>
-      <c r="J42" s="153"/>
-      <c r="K42" s="152"/>
+      <c r="I42" s="115"/>
+      <c r="J42" s="118"/>
+      <c r="K42" s="117"/>
       <c r="L42" s="29"/>
       <c r="M42" s="28"/>
       <c r="N42" s="27">
@@ -5539,9 +5541,9 @@
       <c r="F43" s="34"/>
       <c r="G43" s="38"/>
       <c r="H43" s="32"/>
-      <c r="I43" s="150"/>
-      <c r="J43" s="153"/>
-      <c r="K43" s="152"/>
+      <c r="I43" s="115"/>
+      <c r="J43" s="118"/>
+      <c r="K43" s="117"/>
       <c r="L43" s="29"/>
       <c r="M43" s="28"/>
       <c r="N43" s="27">
@@ -5627,9 +5629,9 @@
       <c r="F44" s="34"/>
       <c r="G44" s="38"/>
       <c r="H44" s="32"/>
-      <c r="I44" s="150"/>
-      <c r="J44" s="153"/>
-      <c r="K44" s="152"/>
+      <c r="I44" s="115"/>
+      <c r="J44" s="118"/>
+      <c r="K44" s="117"/>
       <c r="L44" s="29"/>
       <c r="M44" s="28"/>
       <c r="N44" s="27">
@@ -5715,9 +5717,9 @@
       <c r="F45" s="34"/>
       <c r="G45" s="38"/>
       <c r="H45" s="32"/>
-      <c r="I45" s="150"/>
-      <c r="J45" s="153"/>
-      <c r="K45" s="152"/>
+      <c r="I45" s="115"/>
+      <c r="J45" s="118"/>
+      <c r="K45" s="117"/>
       <c r="L45" s="29"/>
       <c r="M45" s="28"/>
       <c r="N45" s="27">
@@ -5803,9 +5805,9 @@
       <c r="F46" s="34"/>
       <c r="G46" s="38"/>
       <c r="H46" s="32"/>
-      <c r="I46" s="150"/>
-      <c r="J46" s="153"/>
-      <c r="K46" s="152"/>
+      <c r="I46" s="115"/>
+      <c r="J46" s="118"/>
+      <c r="K46" s="117"/>
       <c r="L46" s="29"/>
       <c r="M46" s="28"/>
       <c r="N46" s="27">
@@ -5891,9 +5893,9 @@
       <c r="F47" s="34"/>
       <c r="G47" s="38"/>
       <c r="H47" s="32"/>
-      <c r="I47" s="150"/>
-      <c r="J47" s="153"/>
-      <c r="K47" s="152"/>
+      <c r="I47" s="115"/>
+      <c r="J47" s="118"/>
+      <c r="K47" s="117"/>
       <c r="L47" s="29"/>
       <c r="M47" s="28"/>
       <c r="N47" s="27">
@@ -5979,9 +5981,9 @@
       <c r="F48" s="34"/>
       <c r="G48" s="38"/>
       <c r="H48" s="32"/>
-      <c r="I48" s="150"/>
-      <c r="J48" s="153"/>
-      <c r="K48" s="152"/>
+      <c r="I48" s="115"/>
+      <c r="J48" s="118"/>
+      <c r="K48" s="117"/>
       <c r="L48" s="29"/>
       <c r="M48" s="28"/>
       <c r="N48" s="27">
@@ -6067,9 +6069,9 @@
       <c r="F49" s="34"/>
       <c r="G49" s="38"/>
       <c r="H49" s="32"/>
-      <c r="I49" s="150"/>
-      <c r="J49" s="153"/>
-      <c r="K49" s="152"/>
+      <c r="I49" s="115"/>
+      <c r="J49" s="118"/>
+      <c r="K49" s="117"/>
       <c r="L49" s="29"/>
       <c r="M49" s="28"/>
       <c r="N49" s="27">
@@ -6155,9 +6157,9 @@
       <c r="F50" s="34"/>
       <c r="G50" s="38"/>
       <c r="H50" s="32"/>
-      <c r="I50" s="150"/>
-      <c r="J50" s="153"/>
-      <c r="K50" s="152"/>
+      <c r="I50" s="115"/>
+      <c r="J50" s="118"/>
+      <c r="K50" s="117"/>
       <c r="L50" s="29"/>
       <c r="M50" s="28"/>
       <c r="N50" s="27">
@@ -6243,9 +6245,9 @@
       <c r="F51" s="34"/>
       <c r="G51" s="38"/>
       <c r="H51" s="32"/>
-      <c r="I51" s="150"/>
-      <c r="J51" s="153"/>
-      <c r="K51" s="152"/>
+      <c r="I51" s="115"/>
+      <c r="J51" s="118"/>
+      <c r="K51" s="117"/>
       <c r="L51" s="29"/>
       <c r="M51" s="28"/>
       <c r="N51" s="27">
@@ -6331,9 +6333,9 @@
       <c r="F52" s="34"/>
       <c r="G52" s="38"/>
       <c r="H52" s="32"/>
-      <c r="I52" s="150"/>
-      <c r="J52" s="153"/>
-      <c r="K52" s="152"/>
+      <c r="I52" s="115"/>
+      <c r="J52" s="118"/>
+      <c r="K52" s="117"/>
       <c r="L52" s="29"/>
       <c r="M52" s="28"/>
       <c r="N52" s="27">
@@ -6419,9 +6421,9 @@
       <c r="F53" s="34"/>
       <c r="G53" s="38"/>
       <c r="H53" s="32"/>
-      <c r="I53" s="150"/>
-      <c r="J53" s="153"/>
-      <c r="K53" s="152"/>
+      <c r="I53" s="115"/>
+      <c r="J53" s="118"/>
+      <c r="K53" s="117"/>
       <c r="L53" s="29"/>
       <c r="M53" s="28"/>
       <c r="N53" s="27">
@@ -6507,9 +6509,9 @@
       <c r="F54" s="34"/>
       <c r="G54" s="38"/>
       <c r="H54" s="32"/>
-      <c r="I54" s="150"/>
-      <c r="J54" s="153"/>
-      <c r="K54" s="152"/>
+      <c r="I54" s="115"/>
+      <c r="J54" s="118"/>
+      <c r="K54" s="117"/>
       <c r="L54" s="29"/>
       <c r="M54" s="28"/>
       <c r="N54" s="27">
@@ -6595,9 +6597,9 @@
       <c r="F55" s="34"/>
       <c r="G55" s="38"/>
       <c r="H55" s="32"/>
-      <c r="I55" s="150"/>
-      <c r="J55" s="153"/>
-      <c r="K55" s="152"/>
+      <c r="I55" s="115"/>
+      <c r="J55" s="118"/>
+      <c r="K55" s="117"/>
       <c r="L55" s="29"/>
       <c r="M55" s="28"/>
       <c r="N55" s="27">
@@ -6683,9 +6685,9 @@
       <c r="F56" s="34"/>
       <c r="G56" s="38"/>
       <c r="H56" s="32"/>
-      <c r="I56" s="150"/>
-      <c r="J56" s="153"/>
-      <c r="K56" s="152"/>
+      <c r="I56" s="115"/>
+      <c r="J56" s="118"/>
+      <c r="K56" s="117"/>
       <c r="L56" s="29"/>
       <c r="M56" s="28"/>
       <c r="N56" s="27">
@@ -6771,9 +6773,9 @@
       <c r="F57" s="34"/>
       <c r="G57" s="38"/>
       <c r="H57" s="32"/>
-      <c r="I57" s="150"/>
-      <c r="J57" s="153"/>
-      <c r="K57" s="152"/>
+      <c r="I57" s="115"/>
+      <c r="J57" s="118"/>
+      <c r="K57" s="117"/>
       <c r="L57" s="29"/>
       <c r="M57" s="28"/>
       <c r="N57" s="27">
@@ -6853,15 +6855,15 @@
     <row r="58" spans="1:47" s="37" customFormat="1" ht="47.25" customHeight="1" thickBot="1">
       <c r="A58" s="36"/>
       <c r="B58" s="35"/>
-      <c r="C58" s="149"/>
-      <c r="D58" s="149"/>
-      <c r="E58" s="149"/>
+      <c r="C58" s="114"/>
+      <c r="D58" s="114"/>
+      <c r="E58" s="114"/>
       <c r="F58" s="34"/>
       <c r="G58" s="38"/>
       <c r="H58" s="32"/>
-      <c r="I58" s="150"/>
-      <c r="J58" s="153"/>
-      <c r="K58" s="152"/>
+      <c r="I58" s="115"/>
+      <c r="J58" s="118"/>
+      <c r="K58" s="117"/>
       <c r="L58" s="29"/>
       <c r="M58" s="28"/>
       <c r="N58" s="27">
@@ -6941,15 +6943,15 @@
     <row r="59" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A59" s="36"/>
       <c r="B59" s="35"/>
-      <c r="C59" s="149"/>
-      <c r="D59" s="149"/>
-      <c r="E59" s="149"/>
+      <c r="C59" s="114"/>
+      <c r="D59" s="114"/>
+      <c r="E59" s="114"/>
       <c r="F59" s="34"/>
       <c r="G59" s="38"/>
       <c r="H59" s="32"/>
-      <c r="I59" s="150"/>
-      <c r="J59" s="153"/>
-      <c r="K59" s="152"/>
+      <c r="I59" s="115"/>
+      <c r="J59" s="118"/>
+      <c r="K59" s="117"/>
       <c r="L59" s="29"/>
       <c r="M59" s="28"/>
       <c r="N59" s="27">
@@ -7029,15 +7031,15 @@
     <row r="60" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A60" s="36"/>
       <c r="B60" s="35"/>
-      <c r="C60" s="149"/>
-      <c r="D60" s="149"/>
-      <c r="E60" s="149"/>
+      <c r="C60" s="114"/>
+      <c r="D60" s="114"/>
+      <c r="E60" s="114"/>
       <c r="F60" s="34"/>
       <c r="G60" s="38"/>
       <c r="H60" s="32"/>
-      <c r="I60" s="150"/>
-      <c r="J60" s="153"/>
-      <c r="K60" s="152"/>
+      <c r="I60" s="115"/>
+      <c r="J60" s="118"/>
+      <c r="K60" s="117"/>
       <c r="L60" s="29"/>
       <c r="M60" s="28"/>
       <c r="N60" s="27">
@@ -7117,15 +7119,15 @@
     <row r="61" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A61" s="36"/>
       <c r="B61" s="35"/>
-      <c r="C61" s="149"/>
-      <c r="D61" s="149"/>
-      <c r="E61" s="149"/>
+      <c r="C61" s="114"/>
+      <c r="D61" s="114"/>
+      <c r="E61" s="114"/>
       <c r="F61" s="34"/>
       <c r="G61" s="38"/>
       <c r="H61" s="32"/>
-      <c r="I61" s="150"/>
-      <c r="J61" s="153"/>
-      <c r="K61" s="152"/>
+      <c r="I61" s="115"/>
+      <c r="J61" s="118"/>
+      <c r="K61" s="117"/>
       <c r="L61" s="29"/>
       <c r="M61" s="28"/>
       <c r="N61" s="27">
@@ -7205,15 +7207,15 @@
     <row r="62" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A62" s="36"/>
       <c r="B62" s="35"/>
-      <c r="C62" s="149"/>
-      <c r="D62" s="149"/>
-      <c r="E62" s="149"/>
+      <c r="C62" s="114"/>
+      <c r="D62" s="114"/>
+      <c r="E62" s="114"/>
       <c r="F62" s="34"/>
       <c r="G62" s="38"/>
       <c r="H62" s="32"/>
-      <c r="I62" s="150"/>
-      <c r="J62" s="153"/>
-      <c r="K62" s="152"/>
+      <c r="I62" s="115"/>
+      <c r="J62" s="118"/>
+      <c r="K62" s="117"/>
       <c r="L62" s="29"/>
       <c r="M62" s="28"/>
       <c r="N62" s="27">
@@ -7293,15 +7295,15 @@
     <row r="63" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A63" s="36"/>
       <c r="B63" s="35"/>
-      <c r="C63" s="149"/>
-      <c r="D63" s="149"/>
-      <c r="E63" s="149"/>
+      <c r="C63" s="114"/>
+      <c r="D63" s="114"/>
+      <c r="E63" s="114"/>
       <c r="F63" s="34"/>
       <c r="G63" s="38"/>
       <c r="H63" s="32"/>
-      <c r="I63" s="150"/>
-      <c r="J63" s="153"/>
-      <c r="K63" s="152"/>
+      <c r="I63" s="115"/>
+      <c r="J63" s="118"/>
+      <c r="K63" s="117"/>
       <c r="L63" s="29"/>
       <c r="M63" s="28"/>
       <c r="N63" s="27">
@@ -7381,15 +7383,15 @@
     <row r="64" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A64" s="36"/>
       <c r="B64" s="35"/>
-      <c r="C64" s="149"/>
-      <c r="D64" s="149"/>
-      <c r="E64" s="149"/>
+      <c r="C64" s="114"/>
+      <c r="D64" s="114"/>
+      <c r="E64" s="114"/>
       <c r="F64" s="34"/>
       <c r="G64" s="38"/>
       <c r="H64" s="32"/>
-      <c r="I64" s="150"/>
-      <c r="J64" s="153"/>
-      <c r="K64" s="152"/>
+      <c r="I64" s="115"/>
+      <c r="J64" s="118"/>
+      <c r="K64" s="117"/>
       <c r="L64" s="29"/>
       <c r="M64" s="28"/>
       <c r="N64" s="27">
@@ -7469,15 +7471,15 @@
     <row r="65" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A65" s="36"/>
       <c r="B65" s="35"/>
-      <c r="C65" s="149"/>
-      <c r="D65" s="149"/>
-      <c r="E65" s="149"/>
+      <c r="C65" s="114"/>
+      <c r="D65" s="114"/>
+      <c r="E65" s="114"/>
       <c r="F65" s="34"/>
       <c r="G65" s="38"/>
       <c r="H65" s="32"/>
-      <c r="I65" s="150"/>
-      <c r="J65" s="153"/>
-      <c r="K65" s="152"/>
+      <c r="I65" s="115"/>
+      <c r="J65" s="118"/>
+      <c r="K65" s="117"/>
       <c r="L65" s="29"/>
       <c r="M65" s="28"/>
       <c r="N65" s="27">
@@ -7557,15 +7559,15 @@
     <row r="66" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A66" s="36"/>
       <c r="B66" s="35"/>
-      <c r="C66" s="149"/>
-      <c r="D66" s="149"/>
-      <c r="E66" s="149"/>
+      <c r="C66" s="114"/>
+      <c r="D66" s="114"/>
+      <c r="E66" s="114"/>
       <c r="F66" s="34"/>
       <c r="G66" s="38"/>
       <c r="H66" s="32"/>
-      <c r="I66" s="150"/>
-      <c r="J66" s="153"/>
-      <c r="K66" s="152"/>
+      <c r="I66" s="115"/>
+      <c r="J66" s="118"/>
+      <c r="K66" s="117"/>
       <c r="L66" s="29"/>
       <c r="M66" s="28"/>
       <c r="N66" s="27">
@@ -7645,15 +7647,15 @@
     <row r="67" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A67" s="36"/>
       <c r="B67" s="35"/>
-      <c r="C67" s="149"/>
-      <c r="D67" s="149"/>
-      <c r="E67" s="149"/>
+      <c r="C67" s="114"/>
+      <c r="D67" s="114"/>
+      <c r="E67" s="114"/>
       <c r="F67" s="34"/>
       <c r="G67" s="38"/>
       <c r="H67" s="32"/>
-      <c r="I67" s="150"/>
-      <c r="J67" s="153"/>
-      <c r="K67" s="152"/>
+      <c r="I67" s="115"/>
+      <c r="J67" s="118"/>
+      <c r="K67" s="117"/>
       <c r="L67" s="29"/>
       <c r="M67" s="28"/>
       <c r="N67" s="27">
@@ -7733,15 +7735,15 @@
     <row r="68" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A68" s="36"/>
       <c r="B68" s="35"/>
-      <c r="C68" s="149"/>
-      <c r="D68" s="149"/>
-      <c r="E68" s="149"/>
+      <c r="C68" s="114"/>
+      <c r="D68" s="114"/>
+      <c r="E68" s="114"/>
       <c r="F68" s="34"/>
       <c r="G68" s="38"/>
       <c r="H68" s="32"/>
-      <c r="I68" s="150"/>
-      <c r="J68" s="153"/>
-      <c r="K68" s="152"/>
+      <c r="I68" s="115"/>
+      <c r="J68" s="118"/>
+      <c r="K68" s="117"/>
       <c r="L68" s="29"/>
       <c r="M68" s="28"/>
       <c r="N68" s="27">
@@ -7821,15 +7823,15 @@
     <row r="69" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A69" s="36"/>
       <c r="B69" s="35"/>
-      <c r="C69" s="149"/>
-      <c r="D69" s="149"/>
-      <c r="E69" s="149"/>
+      <c r="C69" s="114"/>
+      <c r="D69" s="114"/>
+      <c r="E69" s="114"/>
       <c r="F69" s="34"/>
       <c r="G69" s="38"/>
       <c r="H69" s="32"/>
-      <c r="I69" s="150"/>
-      <c r="J69" s="153"/>
-      <c r="K69" s="152"/>
+      <c r="I69" s="115"/>
+      <c r="J69" s="118"/>
+      <c r="K69" s="117"/>
       <c r="L69" s="29"/>
       <c r="M69" s="28"/>
       <c r="N69" s="27">
@@ -7909,15 +7911,15 @@
     <row r="70" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A70" s="36"/>
       <c r="B70" s="35"/>
-      <c r="C70" s="149"/>
-      <c r="D70" s="149"/>
-      <c r="E70" s="149"/>
+      <c r="C70" s="114"/>
+      <c r="D70" s="114"/>
+      <c r="E70" s="114"/>
       <c r="F70" s="34"/>
       <c r="G70" s="38"/>
       <c r="H70" s="32"/>
-      <c r="I70" s="150"/>
-      <c r="J70" s="153"/>
-      <c r="K70" s="152"/>
+      <c r="I70" s="115"/>
+      <c r="J70" s="118"/>
+      <c r="K70" s="117"/>
       <c r="L70" s="29"/>
       <c r="M70" s="28"/>
       <c r="N70" s="27">
@@ -7997,15 +7999,15 @@
     <row r="71" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A71" s="36"/>
       <c r="B71" s="35"/>
-      <c r="C71" s="149"/>
-      <c r="D71" s="149"/>
-      <c r="E71" s="149"/>
+      <c r="C71" s="114"/>
+      <c r="D71" s="114"/>
+      <c r="E71" s="114"/>
       <c r="F71" s="34"/>
       <c r="G71" s="38"/>
       <c r="H71" s="32"/>
-      <c r="I71" s="150"/>
-      <c r="J71" s="153"/>
-      <c r="K71" s="152"/>
+      <c r="I71" s="115"/>
+      <c r="J71" s="118"/>
+      <c r="K71" s="117"/>
       <c r="L71" s="29"/>
       <c r="M71" s="28"/>
       <c r="N71" s="27">
@@ -8085,15 +8087,15 @@
     <row r="72" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A72" s="36"/>
       <c r="B72" s="35"/>
-      <c r="C72" s="149"/>
-      <c r="D72" s="149"/>
-      <c r="E72" s="149"/>
+      <c r="C72" s="114"/>
+      <c r="D72" s="114"/>
+      <c r="E72" s="114"/>
       <c r="F72" s="34"/>
       <c r="G72" s="38"/>
       <c r="H72" s="32"/>
-      <c r="I72" s="150"/>
-      <c r="J72" s="153"/>
-      <c r="K72" s="152"/>
+      <c r="I72" s="115"/>
+      <c r="J72" s="118"/>
+      <c r="K72" s="117"/>
       <c r="L72" s="29"/>
       <c r="M72" s="28"/>
       <c r="N72" s="27">
@@ -8173,15 +8175,15 @@
     <row r="73" spans="1:47" s="37" customFormat="1" ht="51.75" customHeight="1" thickBot="1">
       <c r="A73" s="36"/>
       <c r="B73" s="35"/>
-      <c r="C73" s="149"/>
-      <c r="D73" s="149"/>
-      <c r="E73" s="149"/>
+      <c r="C73" s="114"/>
+      <c r="D73" s="114"/>
+      <c r="E73" s="114"/>
       <c r="F73" s="34"/>
       <c r="G73" s="38"/>
       <c r="H73" s="32"/>
-      <c r="I73" s="150"/>
-      <c r="J73" s="153"/>
-      <c r="K73" s="152"/>
+      <c r="I73" s="115"/>
+      <c r="J73" s="118"/>
+      <c r="K73" s="117"/>
       <c r="L73" s="29"/>
       <c r="M73" s="28"/>
       <c r="N73" s="27">
@@ -8261,15 +8263,15 @@
     <row r="74" spans="1:47" s="37" customFormat="1" ht="51.75" customHeight="1" thickBot="1">
       <c r="A74" s="36"/>
       <c r="B74" s="35"/>
-      <c r="C74" s="149"/>
-      <c r="D74" s="149"/>
-      <c r="E74" s="149"/>
+      <c r="C74" s="114"/>
+      <c r="D74" s="114"/>
+      <c r="E74" s="114"/>
       <c r="F74" s="34"/>
       <c r="G74" s="38"/>
       <c r="H74" s="32"/>
-      <c r="I74" s="150"/>
-      <c r="J74" s="153"/>
-      <c r="K74" s="152"/>
+      <c r="I74" s="115"/>
+      <c r="J74" s="118"/>
+      <c r="K74" s="117"/>
       <c r="L74" s="29"/>
       <c r="M74" s="28"/>
       <c r="N74" s="27">
@@ -8349,15 +8351,15 @@
     <row r="75" spans="1:47" s="37" customFormat="1" ht="51.75" customHeight="1" thickBot="1">
       <c r="A75" s="36"/>
       <c r="B75" s="35"/>
-      <c r="C75" s="149"/>
-      <c r="D75" s="149"/>
-      <c r="E75" s="149"/>
+      <c r="C75" s="114"/>
+      <c r="D75" s="114"/>
+      <c r="E75" s="114"/>
       <c r="F75" s="34"/>
       <c r="G75" s="38"/>
       <c r="H75" s="32"/>
-      <c r="I75" s="150"/>
-      <c r="J75" s="153"/>
-      <c r="K75" s="152"/>
+      <c r="I75" s="115"/>
+      <c r="J75" s="118"/>
+      <c r="K75" s="117"/>
       <c r="L75" s="29"/>
       <c r="M75" s="28"/>
       <c r="N75" s="27">
@@ -8437,15 +8439,15 @@
     <row r="76" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A76" s="36"/>
       <c r="B76" s="35"/>
-      <c r="C76" s="149"/>
-      <c r="D76" s="149"/>
-      <c r="E76" s="149"/>
+      <c r="C76" s="114"/>
+      <c r="D76" s="114"/>
+      <c r="E76" s="114"/>
       <c r="F76" s="34"/>
       <c r="G76" s="38"/>
       <c r="H76" s="32"/>
-      <c r="I76" s="150"/>
-      <c r="J76" s="153"/>
-      <c r="K76" s="152"/>
+      <c r="I76" s="115"/>
+      <c r="J76" s="118"/>
+      <c r="K76" s="117"/>
       <c r="L76" s="29"/>
       <c r="M76" s="28"/>
       <c r="N76" s="27">
@@ -8525,15 +8527,15 @@
     <row r="77" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A77" s="36"/>
       <c r="B77" s="35"/>
-      <c r="C77" s="149"/>
-      <c r="D77" s="149"/>
-      <c r="E77" s="149"/>
+      <c r="C77" s="114"/>
+      <c r="D77" s="114"/>
+      <c r="E77" s="114"/>
       <c r="F77" s="34"/>
       <c r="G77" s="38"/>
       <c r="H77" s="32"/>
-      <c r="I77" s="150"/>
-      <c r="J77" s="153"/>
-      <c r="K77" s="152"/>
+      <c r="I77" s="115"/>
+      <c r="J77" s="118"/>
+      <c r="K77" s="117"/>
       <c r="L77" s="29"/>
       <c r="M77" s="28"/>
       <c r="N77" s="27">
@@ -8613,15 +8615,15 @@
     <row r="78" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A78" s="36"/>
       <c r="B78" s="35"/>
-      <c r="C78" s="149"/>
-      <c r="D78" s="149"/>
-      <c r="E78" s="149"/>
+      <c r="C78" s="114"/>
+      <c r="D78" s="114"/>
+      <c r="E78" s="114"/>
       <c r="F78" s="34"/>
       <c r="G78" s="38"/>
       <c r="H78" s="32"/>
-      <c r="I78" s="150"/>
-      <c r="J78" s="153"/>
-      <c r="K78" s="152"/>
+      <c r="I78" s="115"/>
+      <c r="J78" s="118"/>
+      <c r="K78" s="117"/>
       <c r="L78" s="29"/>
       <c r="M78" s="28"/>
       <c r="N78" s="27">
@@ -8701,15 +8703,15 @@
     <row r="79" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A79" s="36"/>
       <c r="B79" s="35"/>
-      <c r="C79" s="149"/>
-      <c r="D79" s="149"/>
-      <c r="E79" s="149"/>
+      <c r="C79" s="114"/>
+      <c r="D79" s="114"/>
+      <c r="E79" s="114"/>
       <c r="F79" s="34"/>
       <c r="G79" s="38"/>
       <c r="H79" s="32"/>
-      <c r="I79" s="150"/>
-      <c r="J79" s="153"/>
-      <c r="K79" s="152"/>
+      <c r="I79" s="115"/>
+      <c r="J79" s="118"/>
+      <c r="K79" s="117"/>
       <c r="L79" s="29"/>
       <c r="M79" s="28"/>
       <c r="N79" s="27">
@@ -8789,15 +8791,15 @@
     <row r="80" spans="1:47" s="37" customFormat="1" ht="47.25" customHeight="1" thickBot="1">
       <c r="A80" s="36"/>
       <c r="B80" s="35"/>
-      <c r="C80" s="149"/>
-      <c r="D80" s="149"/>
-      <c r="E80" s="149"/>
+      <c r="C80" s="114"/>
+      <c r="D80" s="114"/>
+      <c r="E80" s="114"/>
       <c r="F80" s="34"/>
       <c r="G80" s="38"/>
       <c r="H80" s="32"/>
-      <c r="I80" s="150"/>
-      <c r="J80" s="153"/>
-      <c r="K80" s="152"/>
+      <c r="I80" s="115"/>
+      <c r="J80" s="118"/>
+      <c r="K80" s="117"/>
       <c r="L80" s="29"/>
       <c r="M80" s="28"/>
       <c r="N80" s="27">
@@ -8877,15 +8879,15 @@
     <row r="81" spans="1:47" s="37" customFormat="1" ht="47.25" customHeight="1" thickBot="1">
       <c r="A81" s="36"/>
       <c r="B81" s="35"/>
-      <c r="C81" s="149"/>
-      <c r="D81" s="149"/>
-      <c r="E81" s="149"/>
+      <c r="C81" s="114"/>
+      <c r="D81" s="114"/>
+      <c r="E81" s="114"/>
       <c r="F81" s="34"/>
       <c r="G81" s="38"/>
       <c r="H81" s="32"/>
-      <c r="I81" s="150"/>
-      <c r="J81" s="153"/>
-      <c r="K81" s="152"/>
+      <c r="I81" s="115"/>
+      <c r="J81" s="118"/>
+      <c r="K81" s="117"/>
       <c r="L81" s="29"/>
       <c r="M81" s="28"/>
       <c r="N81" s="27">
@@ -8965,15 +8967,15 @@
     <row r="82" spans="1:47" s="37" customFormat="1" ht="47.25" customHeight="1" thickBot="1">
       <c r="A82" s="36"/>
       <c r="B82" s="35"/>
-      <c r="C82" s="149"/>
-      <c r="D82" s="149"/>
-      <c r="E82" s="149"/>
+      <c r="C82" s="114"/>
+      <c r="D82" s="114"/>
+      <c r="E82" s="114"/>
       <c r="F82" s="34"/>
       <c r="G82" s="38"/>
       <c r="H82" s="32"/>
-      <c r="I82" s="150"/>
-      <c r="J82" s="153"/>
-      <c r="K82" s="152"/>
+      <c r="I82" s="115"/>
+      <c r="J82" s="118"/>
+      <c r="K82" s="117"/>
       <c r="L82" s="29"/>
       <c r="M82" s="28"/>
       <c r="N82" s="27">
@@ -9053,15 +9055,15 @@
     <row r="83" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A83" s="36"/>
       <c r="B83" s="35"/>
-      <c r="C83" s="149"/>
-      <c r="D83" s="149"/>
-      <c r="E83" s="149"/>
+      <c r="C83" s="114"/>
+      <c r="D83" s="114"/>
+      <c r="E83" s="114"/>
       <c r="F83" s="34"/>
       <c r="G83" s="38"/>
       <c r="H83" s="32"/>
-      <c r="I83" s="150"/>
-      <c r="J83" s="153"/>
-      <c r="K83" s="152"/>
+      <c r="I83" s="115"/>
+      <c r="J83" s="118"/>
+      <c r="K83" s="117"/>
       <c r="L83" s="29"/>
       <c r="M83" s="28"/>
       <c r="N83" s="27">
@@ -9141,15 +9143,15 @@
     <row r="84" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A84" s="36"/>
       <c r="B84" s="35"/>
-      <c r="C84" s="149"/>
-      <c r="D84" s="149"/>
-      <c r="E84" s="149"/>
+      <c r="C84" s="114"/>
+      <c r="D84" s="114"/>
+      <c r="E84" s="114"/>
       <c r="F84" s="34"/>
       <c r="G84" s="38"/>
       <c r="H84" s="32"/>
-      <c r="I84" s="150"/>
-      <c r="J84" s="153"/>
-      <c r="K84" s="152"/>
+      <c r="I84" s="115"/>
+      <c r="J84" s="118"/>
+      <c r="K84" s="117"/>
       <c r="L84" s="29"/>
       <c r="M84" s="28"/>
       <c r="N84" s="27">
@@ -9229,15 +9231,15 @@
     <row r="85" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A85" s="36"/>
       <c r="B85" s="35"/>
-      <c r="C85" s="149"/>
-      <c r="D85" s="149"/>
-      <c r="E85" s="149"/>
+      <c r="C85" s="114"/>
+      <c r="D85" s="114"/>
+      <c r="E85" s="114"/>
       <c r="F85" s="34"/>
       <c r="G85" s="38"/>
       <c r="H85" s="32"/>
-      <c r="I85" s="150"/>
-      <c r="J85" s="153"/>
-      <c r="K85" s="152"/>
+      <c r="I85" s="115"/>
+      <c r="J85" s="118"/>
+      <c r="K85" s="117"/>
       <c r="L85" s="29"/>
       <c r="M85" s="28"/>
       <c r="N85" s="27">
@@ -9317,15 +9319,15 @@
     <row r="86" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A86" s="36"/>
       <c r="B86" s="35"/>
-      <c r="C86" s="149"/>
-      <c r="D86" s="149"/>
-      <c r="E86" s="149"/>
+      <c r="C86" s="114"/>
+      <c r="D86" s="114"/>
+      <c r="E86" s="114"/>
       <c r="F86" s="34"/>
       <c r="G86" s="38"/>
       <c r="H86" s="32"/>
-      <c r="I86" s="150"/>
-      <c r="J86" s="153"/>
-      <c r="K86" s="152"/>
+      <c r="I86" s="115"/>
+      <c r="J86" s="118"/>
+      <c r="K86" s="117"/>
       <c r="L86" s="29"/>
       <c r="M86" s="28"/>
       <c r="N86" s="27">
@@ -9405,15 +9407,15 @@
     <row r="87" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A87" s="36"/>
       <c r="B87" s="35"/>
-      <c r="C87" s="149"/>
-      <c r="D87" s="149"/>
-      <c r="E87" s="149"/>
+      <c r="C87" s="114"/>
+      <c r="D87" s="114"/>
+      <c r="E87" s="114"/>
       <c r="F87" s="34"/>
       <c r="G87" s="38"/>
       <c r="H87" s="32"/>
-      <c r="I87" s="150"/>
-      <c r="J87" s="153"/>
-      <c r="K87" s="152"/>
+      <c r="I87" s="115"/>
+      <c r="J87" s="118"/>
+      <c r="K87" s="117"/>
       <c r="L87" s="29"/>
       <c r="M87" s="28"/>
       <c r="N87" s="27">
@@ -9493,15 +9495,15 @@
     <row r="88" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A88" s="36"/>
       <c r="B88" s="35"/>
-      <c r="C88" s="149"/>
-      <c r="D88" s="149"/>
-      <c r="E88" s="149"/>
+      <c r="C88" s="114"/>
+      <c r="D88" s="114"/>
+      <c r="E88" s="114"/>
       <c r="F88" s="34"/>
       <c r="G88" s="38"/>
       <c r="H88" s="32"/>
-      <c r="I88" s="150"/>
-      <c r="J88" s="153"/>
-      <c r="K88" s="152"/>
+      <c r="I88" s="115"/>
+      <c r="J88" s="118"/>
+      <c r="K88" s="117"/>
       <c r="L88" s="29"/>
       <c r="M88" s="28"/>
       <c r="N88" s="27">
@@ -9581,15 +9583,15 @@
     <row r="89" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A89" s="36"/>
       <c r="B89" s="35"/>
-      <c r="C89" s="149"/>
-      <c r="D89" s="149"/>
-      <c r="E89" s="149"/>
+      <c r="C89" s="114"/>
+      <c r="D89" s="114"/>
+      <c r="E89" s="114"/>
       <c r="F89" s="34"/>
       <c r="G89" s="38"/>
       <c r="H89" s="32"/>
-      <c r="I89" s="150"/>
-      <c r="J89" s="153"/>
-      <c r="K89" s="152"/>
+      <c r="I89" s="115"/>
+      <c r="J89" s="118"/>
+      <c r="K89" s="117"/>
       <c r="L89" s="29"/>
       <c r="M89" s="28"/>
       <c r="N89" s="27">
@@ -9669,15 +9671,15 @@
     <row r="90" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A90" s="36"/>
       <c r="B90" s="35"/>
-      <c r="C90" s="149"/>
-      <c r="D90" s="149"/>
-      <c r="E90" s="149"/>
+      <c r="C90" s="114"/>
+      <c r="D90" s="114"/>
+      <c r="E90" s="114"/>
       <c r="F90" s="34"/>
       <c r="G90" s="38"/>
       <c r="H90" s="32"/>
-      <c r="I90" s="150"/>
-      <c r="J90" s="153"/>
-      <c r="K90" s="152"/>
+      <c r="I90" s="115"/>
+      <c r="J90" s="118"/>
+      <c r="K90" s="117"/>
       <c r="L90" s="29"/>
       <c r="M90" s="28"/>
       <c r="N90" s="27">
@@ -9757,15 +9759,15 @@
     <row r="91" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A91" s="36"/>
       <c r="B91" s="35"/>
-      <c r="C91" s="149"/>
-      <c r="D91" s="149"/>
-      <c r="E91" s="149"/>
+      <c r="C91" s="114"/>
+      <c r="D91" s="114"/>
+      <c r="E91" s="114"/>
       <c r="F91" s="34"/>
       <c r="G91" s="38"/>
       <c r="H91" s="32"/>
-      <c r="I91" s="150"/>
-      <c r="J91" s="153"/>
-      <c r="K91" s="152"/>
+      <c r="I91" s="115"/>
+      <c r="J91" s="118"/>
+      <c r="K91" s="117"/>
       <c r="L91" s="29"/>
       <c r="M91" s="28"/>
       <c r="N91" s="27">
@@ -9845,15 +9847,15 @@
     <row r="92" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A92" s="36"/>
       <c r="B92" s="35"/>
-      <c r="C92" s="149"/>
-      <c r="D92" s="149"/>
-      <c r="E92" s="149"/>
+      <c r="C92" s="114"/>
+      <c r="D92" s="114"/>
+      <c r="E92" s="114"/>
       <c r="F92" s="34"/>
       <c r="G92" s="38"/>
       <c r="H92" s="32"/>
-      <c r="I92" s="150"/>
-      <c r="J92" s="153"/>
-      <c r="K92" s="152"/>
+      <c r="I92" s="115"/>
+      <c r="J92" s="118"/>
+      <c r="K92" s="117"/>
       <c r="L92" s="29"/>
       <c r="M92" s="28"/>
       <c r="N92" s="27">
@@ -9933,15 +9935,15 @@
     <row r="93" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A93" s="36"/>
       <c r="B93" s="35"/>
-      <c r="C93" s="149"/>
-      <c r="D93" s="149"/>
-      <c r="E93" s="149"/>
+      <c r="C93" s="114"/>
+      <c r="D93" s="114"/>
+      <c r="E93" s="114"/>
       <c r="F93" s="34"/>
       <c r="G93" s="38"/>
       <c r="H93" s="32"/>
-      <c r="I93" s="150"/>
-      <c r="J93" s="153"/>
-      <c r="K93" s="152"/>
+      <c r="I93" s="115"/>
+      <c r="J93" s="118"/>
+      <c r="K93" s="117"/>
       <c r="L93" s="29"/>
       <c r="M93" s="28"/>
       <c r="N93" s="27">
@@ -10021,15 +10023,15 @@
     <row r="94" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A94" s="36"/>
       <c r="B94" s="35"/>
-      <c r="C94" s="149"/>
-      <c r="D94" s="149"/>
-      <c r="E94" s="149"/>
+      <c r="C94" s="114"/>
+      <c r="D94" s="114"/>
+      <c r="E94" s="114"/>
       <c r="F94" s="34"/>
       <c r="G94" s="38"/>
       <c r="H94" s="32"/>
-      <c r="I94" s="150"/>
-      <c r="J94" s="153"/>
-      <c r="K94" s="152"/>
+      <c r="I94" s="115"/>
+      <c r="J94" s="118"/>
+      <c r="K94" s="117"/>
       <c r="L94" s="29"/>
       <c r="M94" s="28"/>
       <c r="N94" s="27">
@@ -10109,15 +10111,15 @@
     <row r="95" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A95" s="36"/>
       <c r="B95" s="35"/>
-      <c r="C95" s="149"/>
-      <c r="D95" s="149"/>
-      <c r="E95" s="149"/>
+      <c r="C95" s="114"/>
+      <c r="D95" s="114"/>
+      <c r="E95" s="114"/>
       <c r="F95" s="34"/>
       <c r="G95" s="38"/>
       <c r="H95" s="32"/>
-      <c r="I95" s="150"/>
-      <c r="J95" s="153"/>
-      <c r="K95" s="152"/>
+      <c r="I95" s="115"/>
+      <c r="J95" s="118"/>
+      <c r="K95" s="117"/>
       <c r="L95" s="29"/>
       <c r="M95" s="28"/>
       <c r="N95" s="27">
@@ -10197,15 +10199,15 @@
     <row r="96" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A96" s="36"/>
       <c r="B96" s="35"/>
-      <c r="C96" s="149"/>
-      <c r="D96" s="149"/>
-      <c r="E96" s="149"/>
+      <c r="C96" s="114"/>
+      <c r="D96" s="114"/>
+      <c r="E96" s="114"/>
       <c r="F96" s="34"/>
       <c r="G96" s="38"/>
       <c r="H96" s="32"/>
-      <c r="I96" s="150"/>
-      <c r="J96" s="153"/>
-      <c r="K96" s="152"/>
+      <c r="I96" s="115"/>
+      <c r="J96" s="118"/>
+      <c r="K96" s="117"/>
       <c r="L96" s="29"/>
       <c r="M96" s="28"/>
       <c r="N96" s="27">
@@ -10285,15 +10287,15 @@
     <row r="97" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A97" s="36"/>
       <c r="B97" s="35"/>
-      <c r="C97" s="149"/>
-      <c r="D97" s="149"/>
-      <c r="E97" s="149"/>
+      <c r="C97" s="114"/>
+      <c r="D97" s="114"/>
+      <c r="E97" s="114"/>
       <c r="F97" s="34"/>
       <c r="G97" s="38"/>
       <c r="H97" s="32"/>
-      <c r="I97" s="150"/>
-      <c r="J97" s="153"/>
-      <c r="K97" s="152"/>
+      <c r="I97" s="115"/>
+      <c r="J97" s="118"/>
+      <c r="K97" s="117"/>
       <c r="L97" s="29"/>
       <c r="M97" s="28"/>
       <c r="N97" s="27">
@@ -10373,15 +10375,15 @@
     <row r="98" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A98" s="36"/>
       <c r="B98" s="35"/>
-      <c r="C98" s="149"/>
-      <c r="D98" s="149"/>
-      <c r="E98" s="149"/>
+      <c r="C98" s="114"/>
+      <c r="D98" s="114"/>
+      <c r="E98" s="114"/>
       <c r="F98" s="34"/>
       <c r="G98" s="38"/>
       <c r="H98" s="32"/>
-      <c r="I98" s="150"/>
-      <c r="J98" s="153"/>
-      <c r="K98" s="152"/>
+      <c r="I98" s="115"/>
+      <c r="J98" s="118"/>
+      <c r="K98" s="117"/>
       <c r="L98" s="29"/>
       <c r="M98" s="28"/>
       <c r="N98" s="27">
@@ -10461,15 +10463,15 @@
     <row r="99" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A99" s="36"/>
       <c r="B99" s="35"/>
-      <c r="C99" s="149"/>
-      <c r="D99" s="149"/>
-      <c r="E99" s="149"/>
+      <c r="C99" s="114"/>
+      <c r="D99" s="114"/>
+      <c r="E99" s="114"/>
       <c r="F99" s="34"/>
       <c r="G99" s="38"/>
       <c r="H99" s="32"/>
-      <c r="I99" s="150"/>
-      <c r="J99" s="153"/>
-      <c r="K99" s="152"/>
+      <c r="I99" s="115"/>
+      <c r="J99" s="118"/>
+      <c r="K99" s="117"/>
       <c r="L99" s="29"/>
       <c r="M99" s="28"/>
       <c r="N99" s="27">
@@ -10549,15 +10551,15 @@
     <row r="100" spans="1:47" s="37" customFormat="1" ht="47.25" customHeight="1" thickBot="1">
       <c r="A100" s="36"/>
       <c r="B100" s="35"/>
-      <c r="C100" s="149"/>
-      <c r="D100" s="149"/>
-      <c r="E100" s="149"/>
+      <c r="C100" s="114"/>
+      <c r="D100" s="114"/>
+      <c r="E100" s="114"/>
       <c r="F100" s="34"/>
       <c r="G100" s="38"/>
       <c r="H100" s="32"/>
-      <c r="I100" s="150"/>
-      <c r="J100" s="153"/>
-      <c r="K100" s="152"/>
+      <c r="I100" s="115"/>
+      <c r="J100" s="118"/>
+      <c r="K100" s="117"/>
       <c r="L100" s="29"/>
       <c r="M100" s="28"/>
       <c r="N100" s="27">
@@ -10637,15 +10639,15 @@
     <row r="101" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A101" s="36"/>
       <c r="B101" s="35"/>
-      <c r="C101" s="149"/>
-      <c r="D101" s="149"/>
-      <c r="E101" s="149"/>
+      <c r="C101" s="114"/>
+      <c r="D101" s="114"/>
+      <c r="E101" s="114"/>
       <c r="F101" s="34"/>
       <c r="G101" s="38"/>
       <c r="H101" s="32"/>
-      <c r="I101" s="150"/>
-      <c r="J101" s="153"/>
-      <c r="K101" s="152"/>
+      <c r="I101" s="115"/>
+      <c r="J101" s="118"/>
+      <c r="K101" s="117"/>
       <c r="L101" s="29"/>
       <c r="M101" s="28"/>
       <c r="N101" s="27">
@@ -10725,15 +10727,15 @@
     <row r="102" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A102" s="36"/>
       <c r="B102" s="35"/>
-      <c r="C102" s="149"/>
-      <c r="D102" s="149"/>
-      <c r="E102" s="149"/>
+      <c r="C102" s="114"/>
+      <c r="D102" s="114"/>
+      <c r="E102" s="114"/>
       <c r="F102" s="34"/>
       <c r="G102" s="38"/>
       <c r="H102" s="32"/>
-      <c r="I102" s="150"/>
-      <c r="J102" s="153"/>
-      <c r="K102" s="152"/>
+      <c r="I102" s="115"/>
+      <c r="J102" s="118"/>
+      <c r="K102" s="117"/>
       <c r="L102" s="29"/>
       <c r="M102" s="28"/>
       <c r="N102" s="27">
@@ -10813,15 +10815,15 @@
     <row r="103" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A103" s="36"/>
       <c r="B103" s="35"/>
-      <c r="C103" s="149"/>
-      <c r="D103" s="149"/>
-      <c r="E103" s="149"/>
+      <c r="C103" s="114"/>
+      <c r="D103" s="114"/>
+      <c r="E103" s="114"/>
       <c r="F103" s="34"/>
       <c r="G103" s="38"/>
       <c r="H103" s="32"/>
-      <c r="I103" s="150"/>
-      <c r="J103" s="153"/>
-      <c r="K103" s="152"/>
+      <c r="I103" s="115"/>
+      <c r="J103" s="118"/>
+      <c r="K103" s="117"/>
       <c r="L103" s="29"/>
       <c r="M103" s="28"/>
       <c r="N103" s="27">
@@ -10901,15 +10903,15 @@
     <row r="104" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A104" s="36"/>
       <c r="B104" s="35"/>
-      <c r="C104" s="149"/>
-      <c r="D104" s="149"/>
-      <c r="E104" s="149"/>
+      <c r="C104" s="114"/>
+      <c r="D104" s="114"/>
+      <c r="E104" s="114"/>
       <c r="F104" s="34"/>
       <c r="G104" s="38"/>
       <c r="H104" s="32"/>
-      <c r="I104" s="150"/>
-      <c r="J104" s="153"/>
-      <c r="K104" s="152"/>
+      <c r="I104" s="115"/>
+      <c r="J104" s="118"/>
+      <c r="K104" s="117"/>
       <c r="L104" s="29"/>
       <c r="M104" s="28"/>
       <c r="N104" s="27">
@@ -10989,15 +10991,15 @@
     <row r="105" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A105" s="36"/>
       <c r="B105" s="35"/>
-      <c r="C105" s="149"/>
-      <c r="D105" s="149"/>
-      <c r="E105" s="149"/>
+      <c r="C105" s="114"/>
+      <c r="D105" s="114"/>
+      <c r="E105" s="114"/>
       <c r="F105" s="34"/>
       <c r="G105" s="38"/>
       <c r="H105" s="32"/>
-      <c r="I105" s="150"/>
-      <c r="J105" s="153"/>
-      <c r="K105" s="152"/>
+      <c r="I105" s="115"/>
+      <c r="J105" s="118"/>
+      <c r="K105" s="117"/>
       <c r="L105" s="29"/>
       <c r="M105" s="28"/>
       <c r="N105" s="27">
@@ -11077,15 +11079,15 @@
     <row r="106" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A106" s="36"/>
       <c r="B106" s="35"/>
-      <c r="C106" s="149"/>
-      <c r="D106" s="149"/>
-      <c r="E106" s="149"/>
+      <c r="C106" s="114"/>
+      <c r="D106" s="114"/>
+      <c r="E106" s="114"/>
       <c r="F106" s="34"/>
       <c r="G106" s="38"/>
       <c r="H106" s="32"/>
-      <c r="I106" s="150"/>
-      <c r="J106" s="153"/>
-      <c r="K106" s="152"/>
+      <c r="I106" s="115"/>
+      <c r="J106" s="118"/>
+      <c r="K106" s="117"/>
       <c r="L106" s="29"/>
       <c r="M106" s="28"/>
       <c r="N106" s="27">
@@ -11165,15 +11167,15 @@
     <row r="107" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A107" s="36"/>
       <c r="B107" s="35"/>
-      <c r="C107" s="149"/>
-      <c r="D107" s="149"/>
-      <c r="E107" s="149"/>
+      <c r="C107" s="114"/>
+      <c r="D107" s="114"/>
+      <c r="E107" s="114"/>
       <c r="F107" s="34"/>
       <c r="G107" s="38"/>
       <c r="H107" s="32"/>
-      <c r="I107" s="150"/>
-      <c r="J107" s="153"/>
-      <c r="K107" s="152"/>
+      <c r="I107" s="115"/>
+      <c r="J107" s="118"/>
+      <c r="K107" s="117"/>
       <c r="L107" s="29"/>
       <c r="M107" s="28"/>
       <c r="N107" s="27">
@@ -11253,15 +11255,15 @@
     <row r="108" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A108" s="36"/>
       <c r="B108" s="35"/>
-      <c r="C108" s="149"/>
-      <c r="D108" s="149"/>
-      <c r="E108" s="149"/>
+      <c r="C108" s="114"/>
+      <c r="D108" s="114"/>
+      <c r="E108" s="114"/>
       <c r="F108" s="34"/>
       <c r="G108" s="38"/>
       <c r="H108" s="32"/>
-      <c r="I108" s="150"/>
-      <c r="J108" s="153"/>
-      <c r="K108" s="152"/>
+      <c r="I108" s="115"/>
+      <c r="J108" s="118"/>
+      <c r="K108" s="117"/>
       <c r="L108" s="29"/>
       <c r="M108" s="28"/>
       <c r="N108" s="27">
@@ -11341,15 +11343,15 @@
     <row r="109" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A109" s="36"/>
       <c r="B109" s="35"/>
-      <c r="C109" s="149"/>
-      <c r="D109" s="149"/>
-      <c r="E109" s="149"/>
+      <c r="C109" s="114"/>
+      <c r="D109" s="114"/>
+      <c r="E109" s="114"/>
       <c r="F109" s="34"/>
       <c r="G109" s="38"/>
       <c r="H109" s="32"/>
-      <c r="I109" s="150"/>
-      <c r="J109" s="153"/>
-      <c r="K109" s="152"/>
+      <c r="I109" s="115"/>
+      <c r="J109" s="118"/>
+      <c r="K109" s="117"/>
       <c r="L109" s="29"/>
       <c r="M109" s="28"/>
       <c r="N109" s="27">
@@ -11429,15 +11431,15 @@
     <row r="110" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A110" s="36"/>
       <c r="B110" s="35"/>
-      <c r="C110" s="149"/>
-      <c r="D110" s="149"/>
-      <c r="E110" s="149"/>
+      <c r="C110" s="114"/>
+      <c r="D110" s="114"/>
+      <c r="E110" s="114"/>
       <c r="F110" s="34"/>
       <c r="G110" s="38"/>
       <c r="H110" s="32"/>
-      <c r="I110" s="150"/>
-      <c r="J110" s="153"/>
-      <c r="K110" s="152"/>
+      <c r="I110" s="115"/>
+      <c r="J110" s="118"/>
+      <c r="K110" s="117"/>
       <c r="L110" s="29"/>
       <c r="M110" s="28"/>
       <c r="N110" s="27">
@@ -11517,15 +11519,15 @@
     <row r="111" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A111" s="36"/>
       <c r="B111" s="35"/>
-      <c r="C111" s="149"/>
-      <c r="D111" s="149"/>
-      <c r="E111" s="149"/>
+      <c r="C111" s="114"/>
+      <c r="D111" s="114"/>
+      <c r="E111" s="114"/>
       <c r="F111" s="34"/>
       <c r="G111" s="38"/>
       <c r="H111" s="32"/>
-      <c r="I111" s="150"/>
-      <c r="J111" s="153"/>
-      <c r="K111" s="152"/>
+      <c r="I111" s="115"/>
+      <c r="J111" s="118"/>
+      <c r="K111" s="117"/>
       <c r="L111" s="29"/>
       <c r="M111" s="28"/>
       <c r="N111" s="27">
@@ -11605,15 +11607,15 @@
     <row r="112" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A112" s="36"/>
       <c r="B112" s="35"/>
-      <c r="C112" s="149"/>
-      <c r="D112" s="149"/>
-      <c r="E112" s="149"/>
+      <c r="C112" s="114"/>
+      <c r="D112" s="114"/>
+      <c r="E112" s="114"/>
       <c r="F112" s="34"/>
       <c r="G112" s="38"/>
       <c r="H112" s="32"/>
-      <c r="I112" s="150"/>
-      <c r="J112" s="153"/>
-      <c r="K112" s="152"/>
+      <c r="I112" s="115"/>
+      <c r="J112" s="118"/>
+      <c r="K112" s="117"/>
       <c r="L112" s="29"/>
       <c r="M112" s="28"/>
       <c r="N112" s="27">
@@ -11693,15 +11695,15 @@
     <row r="113" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A113" s="36"/>
       <c r="B113" s="35"/>
-      <c r="C113" s="149"/>
-      <c r="D113" s="149"/>
-      <c r="E113" s="149"/>
+      <c r="C113" s="114"/>
+      <c r="D113" s="114"/>
+      <c r="E113" s="114"/>
       <c r="F113" s="34"/>
       <c r="G113" s="38"/>
       <c r="H113" s="32"/>
-      <c r="I113" s="150"/>
-      <c r="J113" s="153"/>
-      <c r="K113" s="152"/>
+      <c r="I113" s="115"/>
+      <c r="J113" s="118"/>
+      <c r="K113" s="117"/>
       <c r="L113" s="29"/>
       <c r="M113" s="28"/>
       <c r="N113" s="27">
@@ -11781,15 +11783,15 @@
     <row r="114" spans="1:47" s="37" customFormat="1" ht="47.25" customHeight="1" thickBot="1">
       <c r="A114" s="36"/>
       <c r="B114" s="35"/>
-      <c r="C114" s="149"/>
-      <c r="D114" s="149"/>
-      <c r="E114" s="149"/>
+      <c r="C114" s="114"/>
+      <c r="D114" s="114"/>
+      <c r="E114" s="114"/>
       <c r="F114" s="34"/>
       <c r="G114" s="38"/>
       <c r="H114" s="32"/>
-      <c r="I114" s="150"/>
-      <c r="J114" s="153"/>
-      <c r="K114" s="152"/>
+      <c r="I114" s="115"/>
+      <c r="J114" s="118"/>
+      <c r="K114" s="117"/>
       <c r="L114" s="29"/>
       <c r="M114" s="28"/>
       <c r="N114" s="27">
@@ -11869,15 +11871,15 @@
     <row r="115" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A115" s="36"/>
       <c r="B115" s="35"/>
-      <c r="C115" s="149"/>
-      <c r="D115" s="149"/>
-      <c r="E115" s="149"/>
+      <c r="C115" s="114"/>
+      <c r="D115" s="114"/>
+      <c r="E115" s="114"/>
       <c r="F115" s="34"/>
       <c r="G115" s="38"/>
       <c r="H115" s="32"/>
-      <c r="I115" s="150"/>
-      <c r="J115" s="153"/>
-      <c r="K115" s="152"/>
+      <c r="I115" s="115"/>
+      <c r="J115" s="118"/>
+      <c r="K115" s="117"/>
       <c r="L115" s="29"/>
       <c r="M115" s="28"/>
       <c r="N115" s="27">
@@ -11957,15 +11959,15 @@
     <row r="116" spans="1:47" s="37" customFormat="1" ht="47.25" customHeight="1" thickBot="1">
       <c r="A116" s="36"/>
       <c r="B116" s="35"/>
-      <c r="C116" s="149"/>
-      <c r="D116" s="149"/>
-      <c r="E116" s="149"/>
+      <c r="C116" s="114"/>
+      <c r="D116" s="114"/>
+      <c r="E116" s="114"/>
       <c r="F116" s="34"/>
       <c r="G116" s="38"/>
       <c r="H116" s="32"/>
-      <c r="I116" s="150"/>
-      <c r="J116" s="153"/>
-      <c r="K116" s="152"/>
+      <c r="I116" s="115"/>
+      <c r="J116" s="118"/>
+      <c r="K116" s="117"/>
       <c r="L116" s="29"/>
       <c r="M116" s="28"/>
       <c r="N116" s="27">
@@ -12045,15 +12047,15 @@
     <row r="117" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A117" s="36"/>
       <c r="B117" s="35"/>
-      <c r="C117" s="149"/>
-      <c r="D117" s="149"/>
-      <c r="E117" s="149"/>
+      <c r="C117" s="114"/>
+      <c r="D117" s="114"/>
+      <c r="E117" s="114"/>
       <c r="F117" s="34"/>
       <c r="G117" s="38"/>
       <c r="H117" s="32"/>
-      <c r="I117" s="150"/>
-      <c r="J117" s="153"/>
-      <c r="K117" s="152"/>
+      <c r="I117" s="115"/>
+      <c r="J117" s="118"/>
+      <c r="K117" s="117"/>
       <c r="L117" s="29"/>
       <c r="M117" s="28"/>
       <c r="N117" s="27">
@@ -12133,15 +12135,15 @@
     <row r="118" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A118" s="36"/>
       <c r="B118" s="35"/>
-      <c r="C118" s="149"/>
-      <c r="D118" s="149"/>
-      <c r="E118" s="149"/>
+      <c r="C118" s="114"/>
+      <c r="D118" s="114"/>
+      <c r="E118" s="114"/>
       <c r="F118" s="34"/>
       <c r="G118" s="38"/>
       <c r="H118" s="32"/>
-      <c r="I118" s="150"/>
-      <c r="J118" s="153"/>
-      <c r="K118" s="152"/>
+      <c r="I118" s="115"/>
+      <c r="J118" s="118"/>
+      <c r="K118" s="117"/>
       <c r="L118" s="29"/>
       <c r="M118" s="28"/>
       <c r="N118" s="27">
@@ -12221,15 +12223,15 @@
     <row r="119" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A119" s="36"/>
       <c r="B119" s="35"/>
-      <c r="C119" s="149"/>
-      <c r="D119" s="149"/>
-      <c r="E119" s="149"/>
+      <c r="C119" s="114"/>
+      <c r="D119" s="114"/>
+      <c r="E119" s="114"/>
       <c r="F119" s="34"/>
       <c r="G119" s="38"/>
       <c r="H119" s="32"/>
-      <c r="I119" s="150"/>
-      <c r="J119" s="153"/>
-      <c r="K119" s="152"/>
+      <c r="I119" s="115"/>
+      <c r="J119" s="118"/>
+      <c r="K119" s="117"/>
       <c r="L119" s="29"/>
       <c r="M119" s="28"/>
       <c r="N119" s="27">
@@ -12309,15 +12311,15 @@
     <row r="120" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A120" s="36"/>
       <c r="B120" s="35"/>
-      <c r="C120" s="149"/>
-      <c r="D120" s="149"/>
-      <c r="E120" s="149"/>
+      <c r="C120" s="114"/>
+      <c r="D120" s="114"/>
+      <c r="E120" s="114"/>
       <c r="F120" s="34"/>
       <c r="G120" s="38"/>
       <c r="H120" s="32"/>
-      <c r="I120" s="150"/>
-      <c r="J120" s="153"/>
-      <c r="K120" s="152"/>
+      <c r="I120" s="115"/>
+      <c r="J120" s="118"/>
+      <c r="K120" s="117"/>
       <c r="L120" s="29"/>
       <c r="M120" s="28"/>
       <c r="N120" s="27">
@@ -12397,15 +12399,15 @@
     <row r="121" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A121" s="36"/>
       <c r="B121" s="35"/>
-      <c r="C121" s="149"/>
-      <c r="D121" s="149"/>
-      <c r="E121" s="149"/>
+      <c r="C121" s="114"/>
+      <c r="D121" s="114"/>
+      <c r="E121" s="114"/>
       <c r="F121" s="34"/>
       <c r="G121" s="33"/>
       <c r="H121" s="32"/>
-      <c r="I121" s="150"/>
-      <c r="J121" s="153"/>
-      <c r="K121" s="152"/>
+      <c r="I121" s="115"/>
+      <c r="J121" s="118"/>
+      <c r="K121" s="117"/>
       <c r="L121" s="29"/>
       <c r="M121" s="28"/>
       <c r="N121" s="27">
@@ -12485,15 +12487,15 @@
     <row r="122" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A122" s="36"/>
       <c r="B122" s="35"/>
-      <c r="C122" s="149"/>
-      <c r="D122" s="149"/>
-      <c r="E122" s="149"/>
+      <c r="C122" s="114"/>
+      <c r="D122" s="114"/>
+      <c r="E122" s="114"/>
       <c r="F122" s="34"/>
       <c r="G122" s="33"/>
       <c r="H122" s="32"/>
-      <c r="I122" s="150"/>
-      <c r="J122" s="153"/>
-      <c r="K122" s="152"/>
+      <c r="I122" s="115"/>
+      <c r="J122" s="118"/>
+      <c r="K122" s="117"/>
       <c r="L122" s="29"/>
       <c r="M122" s="28"/>
       <c r="N122" s="27">
@@ -12573,15 +12575,15 @@
     <row r="123" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A123" s="36"/>
       <c r="B123" s="35"/>
-      <c r="C123" s="149"/>
-      <c r="D123" s="149"/>
-      <c r="E123" s="149"/>
+      <c r="C123" s="114"/>
+      <c r="D123" s="114"/>
+      <c r="E123" s="114"/>
       <c r="F123" s="34"/>
       <c r="G123" s="33"/>
       <c r="H123" s="32"/>
-      <c r="I123" s="150"/>
-      <c r="J123" s="153"/>
-      <c r="K123" s="152"/>
+      <c r="I123" s="115"/>
+      <c r="J123" s="118"/>
+      <c r="K123" s="117"/>
       <c r="L123" s="29"/>
       <c r="M123" s="28"/>
       <c r="N123" s="27">
@@ -12661,15 +12663,15 @@
     <row r="124" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A124" s="36"/>
       <c r="B124" s="35"/>
-      <c r="C124" s="149"/>
-      <c r="D124" s="149"/>
-      <c r="E124" s="149"/>
+      <c r="C124" s="114"/>
+      <c r="D124" s="114"/>
+      <c r="E124" s="114"/>
       <c r="F124" s="34"/>
       <c r="G124" s="33"/>
       <c r="H124" s="32"/>
-      <c r="I124" s="150"/>
-      <c r="J124" s="153"/>
-      <c r="K124" s="152"/>
+      <c r="I124" s="115"/>
+      <c r="J124" s="118"/>
+      <c r="K124" s="117"/>
       <c r="L124" s="29"/>
       <c r="M124" s="28"/>
       <c r="N124" s="27">
@@ -12749,15 +12751,15 @@
     <row r="125" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A125" s="36"/>
       <c r="B125" s="35"/>
-      <c r="C125" s="149"/>
-      <c r="D125" s="149"/>
-      <c r="E125" s="149"/>
+      <c r="C125" s="114"/>
+      <c r="D125" s="114"/>
+      <c r="E125" s="114"/>
       <c r="F125" s="34"/>
       <c r="G125" s="33"/>
       <c r="H125" s="32"/>
-      <c r="I125" s="150"/>
-      <c r="J125" s="153"/>
-      <c r="K125" s="152"/>
+      <c r="I125" s="115"/>
+      <c r="J125" s="118"/>
+      <c r="K125" s="117"/>
       <c r="L125" s="29"/>
       <c r="M125" s="28"/>
       <c r="N125" s="27">
@@ -12837,15 +12839,15 @@
     <row r="126" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A126" s="36"/>
       <c r="B126" s="35"/>
-      <c r="C126" s="149"/>
-      <c r="D126" s="149"/>
-      <c r="E126" s="149"/>
+      <c r="C126" s="114"/>
+      <c r="D126" s="114"/>
+      <c r="E126" s="114"/>
       <c r="F126" s="34"/>
       <c r="G126" s="33"/>
       <c r="H126" s="32"/>
-      <c r="I126" s="150"/>
-      <c r="J126" s="153"/>
-      <c r="K126" s="152"/>
+      <c r="I126" s="115"/>
+      <c r="J126" s="118"/>
+      <c r="K126" s="117"/>
       <c r="L126" s="29"/>
       <c r="M126" s="28"/>
       <c r="N126" s="27">
@@ -12925,15 +12927,15 @@
     <row r="127" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A127" s="36"/>
       <c r="B127" s="35"/>
-      <c r="C127" s="149"/>
-      <c r="D127" s="149"/>
-      <c r="E127" s="149"/>
+      <c r="C127" s="114"/>
+      <c r="D127" s="114"/>
+      <c r="E127" s="114"/>
       <c r="F127" s="34"/>
       <c r="G127" s="33"/>
       <c r="H127" s="32"/>
-      <c r="I127" s="150"/>
-      <c r="J127" s="153"/>
-      <c r="K127" s="152"/>
+      <c r="I127" s="115"/>
+      <c r="J127" s="118"/>
+      <c r="K127" s="117"/>
       <c r="L127" s="29"/>
       <c r="M127" s="28"/>
       <c r="N127" s="27">
@@ -13013,15 +13015,15 @@
     <row r="128" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A128" s="36"/>
       <c r="B128" s="35"/>
-      <c r="C128" s="149"/>
-      <c r="D128" s="149"/>
-      <c r="E128" s="149"/>
+      <c r="C128" s="114"/>
+      <c r="D128" s="114"/>
+      <c r="E128" s="114"/>
       <c r="F128" s="34"/>
       <c r="G128" s="33"/>
       <c r="H128" s="32"/>
-      <c r="I128" s="150"/>
-      <c r="J128" s="153"/>
-      <c r="K128" s="152"/>
+      <c r="I128" s="115"/>
+      <c r="J128" s="118"/>
+      <c r="K128" s="117"/>
       <c r="L128" s="29"/>
       <c r="M128" s="28"/>
       <c r="N128" s="27">
@@ -13101,15 +13103,15 @@
     <row r="129" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A129" s="36"/>
       <c r="B129" s="35"/>
-      <c r="C129" s="149"/>
-      <c r="D129" s="149"/>
-      <c r="E129" s="149"/>
+      <c r="C129" s="114"/>
+      <c r="D129" s="114"/>
+      <c r="E129" s="114"/>
       <c r="F129" s="34"/>
       <c r="G129" s="33"/>
       <c r="H129" s="32"/>
-      <c r="I129" s="150"/>
-      <c r="J129" s="153"/>
-      <c r="K129" s="152"/>
+      <c r="I129" s="115"/>
+      <c r="J129" s="118"/>
+      <c r="K129" s="117"/>
       <c r="L129" s="29"/>
       <c r="M129" s="28"/>
       <c r="N129" s="27">
@@ -13189,15 +13191,15 @@
     <row r="130" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A130" s="36"/>
       <c r="B130" s="35"/>
-      <c r="C130" s="149"/>
-      <c r="D130" s="149"/>
-      <c r="E130" s="149"/>
+      <c r="C130" s="114"/>
+      <c r="D130" s="114"/>
+      <c r="E130" s="114"/>
       <c r="F130" s="34"/>
       <c r="G130" s="33"/>
       <c r="H130" s="32"/>
-      <c r="I130" s="150"/>
-      <c r="J130" s="153"/>
-      <c r="K130" s="152"/>
+      <c r="I130" s="115"/>
+      <c r="J130" s="118"/>
+      <c r="K130" s="117"/>
       <c r="L130" s="29"/>
       <c r="M130" s="28"/>
       <c r="N130" s="27">
@@ -13277,15 +13279,15 @@
     <row r="131" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A131" s="36"/>
       <c r="B131" s="35"/>
-      <c r="C131" s="149"/>
-      <c r="D131" s="149"/>
-      <c r="E131" s="149"/>
+      <c r="C131" s="114"/>
+      <c r="D131" s="114"/>
+      <c r="E131" s="114"/>
       <c r="F131" s="34"/>
       <c r="G131" s="33"/>
       <c r="H131" s="32"/>
-      <c r="I131" s="150"/>
-      <c r="J131" s="153"/>
-      <c r="K131" s="152"/>
+      <c r="I131" s="115"/>
+      <c r="J131" s="118"/>
+      <c r="K131" s="117"/>
       <c r="L131" s="29"/>
       <c r="M131" s="28"/>
       <c r="N131" s="27">
@@ -13365,15 +13367,15 @@
     <row r="132" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A132" s="36"/>
       <c r="B132" s="35"/>
-      <c r="C132" s="149"/>
-      <c r="D132" s="149"/>
-      <c r="E132" s="149"/>
+      <c r="C132" s="114"/>
+      <c r="D132" s="114"/>
+      <c r="E132" s="114"/>
       <c r="F132" s="34"/>
       <c r="G132" s="33"/>
       <c r="H132" s="32"/>
-      <c r="I132" s="150"/>
-      <c r="J132" s="153"/>
-      <c r="K132" s="152"/>
+      <c r="I132" s="115"/>
+      <c r="J132" s="118"/>
+      <c r="K132" s="117"/>
       <c r="L132" s="29"/>
       <c r="M132" s="28"/>
       <c r="N132" s="27">
@@ -13453,15 +13455,15 @@
     <row r="133" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A133" s="36"/>
       <c r="B133" s="35"/>
-      <c r="C133" s="149"/>
-      <c r="D133" s="149"/>
-      <c r="E133" s="149"/>
+      <c r="C133" s="114"/>
+      <c r="D133" s="114"/>
+      <c r="E133" s="114"/>
       <c r="F133" s="34"/>
       <c r="G133" s="33"/>
       <c r="H133" s="32"/>
-      <c r="I133" s="150"/>
-      <c r="J133" s="153"/>
-      <c r="K133" s="152"/>
+      <c r="I133" s="115"/>
+      <c r="J133" s="118"/>
+      <c r="K133" s="117"/>
       <c r="L133" s="29"/>
       <c r="M133" s="28"/>
       <c r="N133" s="27">
@@ -13541,15 +13543,15 @@
     <row r="134" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A134" s="36"/>
       <c r="B134" s="35"/>
-      <c r="C134" s="149"/>
-      <c r="D134" s="149"/>
-      <c r="E134" s="149"/>
+      <c r="C134" s="114"/>
+      <c r="D134" s="114"/>
+      <c r="E134" s="114"/>
       <c r="F134" s="34"/>
       <c r="G134" s="33"/>
       <c r="H134" s="32"/>
-      <c r="I134" s="150"/>
-      <c r="J134" s="153"/>
-      <c r="K134" s="152"/>
+      <c r="I134" s="115"/>
+      <c r="J134" s="118"/>
+      <c r="K134" s="117"/>
       <c r="L134" s="29"/>
       <c r="M134" s="28"/>
       <c r="N134" s="27">
@@ -13629,15 +13631,15 @@
     <row r="135" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A135" s="36"/>
       <c r="B135" s="35"/>
-      <c r="C135" s="149"/>
-      <c r="D135" s="149"/>
-      <c r="E135" s="149"/>
+      <c r="C135" s="114"/>
+      <c r="D135" s="114"/>
+      <c r="E135" s="114"/>
       <c r="F135" s="34"/>
       <c r="G135" s="33"/>
       <c r="H135" s="32"/>
-      <c r="I135" s="150"/>
-      <c r="J135" s="153"/>
-      <c r="K135" s="152"/>
+      <c r="I135" s="115"/>
+      <c r="J135" s="118"/>
+      <c r="K135" s="117"/>
       <c r="L135" s="29"/>
       <c r="M135" s="28"/>
       <c r="N135" s="27">
@@ -13717,15 +13719,15 @@
     <row r="136" spans="1:47" s="37" customFormat="1" ht="47.25" customHeight="1" thickBot="1">
       <c r="A136" s="36"/>
       <c r="B136" s="35"/>
-      <c r="C136" s="149"/>
-      <c r="D136" s="149"/>
-      <c r="E136" s="149"/>
+      <c r="C136" s="114"/>
+      <c r="D136" s="114"/>
+      <c r="E136" s="114"/>
       <c r="F136" s="34"/>
       <c r="G136" s="33"/>
       <c r="H136" s="32"/>
-      <c r="I136" s="150"/>
-      <c r="J136" s="153"/>
-      <c r="K136" s="152"/>
+      <c r="I136" s="115"/>
+      <c r="J136" s="118"/>
+      <c r="K136" s="117"/>
       <c r="L136" s="29"/>
       <c r="M136" s="28"/>
       <c r="N136" s="27">
@@ -13805,15 +13807,15 @@
     <row r="137" spans="1:47" s="37" customFormat="1" ht="36" customHeight="1" thickBot="1">
       <c r="A137" s="36"/>
       <c r="B137" s="35"/>
-      <c r="C137" s="149"/>
-      <c r="D137" s="149"/>
-      <c r="E137" s="149"/>
+      <c r="C137" s="114"/>
+      <c r="D137" s="114"/>
+      <c r="E137" s="114"/>
       <c r="F137" s="34"/>
       <c r="G137" s="33"/>
       <c r="H137" s="32"/>
-      <c r="I137" s="150"/>
-      <c r="J137" s="153"/>
-      <c r="K137" s="152"/>
+      <c r="I137" s="115"/>
+      <c r="J137" s="118"/>
+      <c r="K137" s="117"/>
       <c r="L137" s="29"/>
       <c r="M137" s="28"/>
       <c r="N137" s="27">
@@ -13899,9 +13901,9 @@
       <c r="F138" s="34"/>
       <c r="G138" s="33"/>
       <c r="H138" s="32"/>
-      <c r="I138" s="150"/>
-      <c r="J138" s="153"/>
-      <c r="K138" s="152"/>
+      <c r="I138" s="115"/>
+      <c r="J138" s="118"/>
+      <c r="K138" s="117"/>
       <c r="L138" s="29"/>
       <c r="M138" s="28"/>
       <c r="N138" s="27">
@@ -13987,9 +13989,9 @@
       <c r="F139" s="34"/>
       <c r="G139" s="33"/>
       <c r="H139" s="32"/>
-      <c r="I139" s="150"/>
-      <c r="J139" s="153"/>
-      <c r="K139" s="152"/>
+      <c r="I139" s="115"/>
+      <c r="J139" s="118"/>
+      <c r="K139" s="117"/>
       <c r="L139" s="29"/>
       <c r="M139" s="28"/>
       <c r="N139" s="27">
@@ -14075,9 +14077,9 @@
       <c r="F140" s="34"/>
       <c r="G140" s="33"/>
       <c r="H140" s="32"/>
-      <c r="I140" s="150"/>
-      <c r="J140" s="153"/>
-      <c r="K140" s="152"/>
+      <c r="I140" s="115"/>
+      <c r="J140" s="118"/>
+      <c r="K140" s="117"/>
       <c r="L140" s="29"/>
       <c r="M140" s="28"/>
       <c r="N140" s="27">
@@ -14163,9 +14165,9 @@
       <c r="F141" s="34"/>
       <c r="G141" s="33"/>
       <c r="H141" s="32"/>
-      <c r="I141" s="150"/>
-      <c r="J141" s="153"/>
-      <c r="K141" s="152"/>
+      <c r="I141" s="115"/>
+      <c r="J141" s="118"/>
+      <c r="K141" s="117"/>
       <c r="L141" s="29"/>
       <c r="M141" s="28"/>
       <c r="N141" s="27">
@@ -14251,9 +14253,9 @@
       <c r="F142" s="34"/>
       <c r="G142" s="33"/>
       <c r="H142" s="32"/>
-      <c r="I142" s="150"/>
-      <c r="J142" s="153"/>
-      <c r="K142" s="152"/>
+      <c r="I142" s="115"/>
+      <c r="J142" s="118"/>
+      <c r="K142" s="117"/>
       <c r="L142" s="29"/>
       <c r="M142" s="28"/>
       <c r="N142" s="27">
@@ -14339,9 +14341,9 @@
       <c r="F143" s="34"/>
       <c r="G143" s="33"/>
       <c r="H143" s="32"/>
-      <c r="I143" s="150"/>
-      <c r="J143" s="153"/>
-      <c r="K143" s="152"/>
+      <c r="I143" s="115"/>
+      <c r="J143" s="118"/>
+      <c r="K143" s="117"/>
       <c r="L143" s="29"/>
       <c r="M143" s="28"/>
       <c r="N143" s="27">
@@ -14427,9 +14429,9 @@
       <c r="F144" s="34"/>
       <c r="G144" s="33"/>
       <c r="H144" s="32"/>
-      <c r="I144" s="150"/>
-      <c r="J144" s="153"/>
-      <c r="K144" s="152"/>
+      <c r="I144" s="115"/>
+      <c r="J144" s="118"/>
+      <c r="K144" s="117"/>
       <c r="L144" s="29"/>
       <c r="M144" s="28"/>
       <c r="N144" s="27">
@@ -14515,9 +14517,9 @@
       <c r="F145" s="34"/>
       <c r="G145" s="33"/>
       <c r="H145" s="32"/>
-      <c r="I145" s="150"/>
-      <c r="J145" s="153"/>
-      <c r="K145" s="152"/>
+      <c r="I145" s="115"/>
+      <c r="J145" s="118"/>
+      <c r="K145" s="117"/>
       <c r="L145" s="29"/>
       <c r="M145" s="28"/>
       <c r="N145" s="27">
@@ -14596,14 +14598,14 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="AT3:AT4"/>
-    <mergeCell ref="AU3:AU4"/>
-    <mergeCell ref="AN3:AN4"/>
-    <mergeCell ref="AO3:AO4"/>
-    <mergeCell ref="AP3:AP4"/>
-    <mergeCell ref="AQ3:AQ4"/>
-    <mergeCell ref="AR3:AR4"/>
-    <mergeCell ref="AS3:AS4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="N1:AH1"/>
+    <mergeCell ref="AI1:AL1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="P2:U2"/>
     <mergeCell ref="AM3:AM4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -14616,14 +14618,14 @@
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="N1:AH1"/>
-    <mergeCell ref="AI1:AL1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="P2:U2"/>
+    <mergeCell ref="AT3:AT4"/>
+    <mergeCell ref="AU3:AU4"/>
+    <mergeCell ref="AN3:AN4"/>
+    <mergeCell ref="AO3:AO4"/>
+    <mergeCell ref="AP3:AP4"/>
+    <mergeCell ref="AQ3:AQ4"/>
+    <mergeCell ref="AR3:AR4"/>
+    <mergeCell ref="AS3:AS4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
